--- a/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_variable_hrp_monthly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_variable_hrp_monthly.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU10"/>
+  <dimension ref="A1:AU9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -956,12 +956,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -982,38 +982,42 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>39442</v>
+        <v>43880</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>39881</v>
+        <v>44846</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>40533</v>
+        <v>45912</v>
       </c>
       <c r="M4" t="n">
-        <v>753</v>
+        <v>1399</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.3744774130256877</v>
+        <v>-0.3839136556212107</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.3744774130256877</v>
+        <v>-0.3839136556212107</v>
       </c>
       <c r="P4" t="n">
-        <v>752</v>
+        <v>1398</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.1599384989554068</v>
+        <v>0.2272090031896818</v>
       </c>
       <c r="R4" t="b">
         <v>0</v>
@@ -1023,25 +1027,25 @@
       </c>
       <c r="T4" s="3" t="inlineStr"/>
       <c r="U4" t="n">
-        <v>301</v>
+        <v>668</v>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" s="3" t="n">
-        <v>-0.3744774130256877</v>
+        <v>-0.3839136556212107</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>-0.3744774130256877</v>
+        <v>-0.3839136556212107</v>
       </c>
       <c r="Y4" t="b">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>452</v>
+        <v>731</v>
       </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" s="3" t="n">
-        <v>0.5986632950171407</v>
+        <v>0.6231491074653142</v>
       </c>
       <c r="AD4" s="3" t="n">
         <v>0.8333333333333334</v>
@@ -1052,19 +1056,19 @@
         </is>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="AH4" s="3" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="AJ4" s="3" t="n">
@@ -1076,11 +1080,11 @@
         </is>
       </c>
       <c r="AL4" s="3" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="AN4" s="3" t="n">
@@ -1106,7 +1110,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1137,32 +1141,32 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>43880</v>
+        <v>39442</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>44846</v>
+        <v>39881</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>45912</v>
+        <v>40533</v>
       </c>
       <c r="M5" t="n">
-        <v>1399</v>
+        <v>753</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.3839136556212107</v>
+        <v>-0.3744774130256879</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.3839136556212107</v>
+        <v>-0.3744774130256879</v>
       </c>
       <c r="P5" t="n">
-        <v>1398</v>
+        <v>752</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.2272090031896818</v>
+        <v>0.1599384989554069</v>
       </c>
       <c r="R5" t="b">
         <v>0</v>
@@ -1172,25 +1176,25 @@
       </c>
       <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>668</v>
+        <v>301</v>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" s="3" t="n">
-        <v>-0.3839136556212107</v>
+        <v>-0.3744774130256879</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>-0.3839136556212107</v>
+        <v>-0.3744774130256879</v>
       </c>
       <c r="Y5" t="b">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>731</v>
+        <v>452</v>
       </c>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" s="3" t="n">
-        <v>0.6231491074653142</v>
+        <v>0.5986632950171411</v>
       </c>
       <c r="AD5" s="3" t="n">
         <v>0.8333333333333334</v>
@@ -1209,35 +1213,35 @@
         </is>
       </c>
       <c r="AH5" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="AJ5" s="3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>2/6</t>
+        </is>
+      </c>
+      <c r="AL5" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="AK5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>3/6</t>
         </is>
       </c>
-      <c r="AL5" s="3" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>4/6</t>
-        </is>
-      </c>
       <c r="AN5" s="3" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AP5" s="3" t="inlineStr"/>
@@ -1255,7 +1259,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1273,49 +1277,45 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>39442</v>
+        <v>36865</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>39881</v>
+        <v>37460</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>40533</v>
+        <v>39275</v>
       </c>
       <c r="M6" t="n">
-        <v>753</v>
+        <v>1656</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.3744774130256879</v>
+        <v>-0.4206842640084347</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.3744774130256879</v>
+        <v>-0.4206842640084347</v>
       </c>
       <c r="P6" t="n">
-        <v>752</v>
+        <v>1655</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.1599384989554069</v>
+        <v>0.2271324373454977</v>
       </c>
       <c r="R6" t="b">
         <v>0</v>
@@ -1325,40 +1325,40 @@
       </c>
       <c r="T6" s="3" t="inlineStr"/>
       <c r="U6" t="n">
-        <v>301</v>
+        <v>405</v>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" s="3" t="n">
-        <v>-0.3744774130256879</v>
+        <v>-0.4206842640084347</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-0.3744774130256879</v>
+        <v>-0.4206842640084347</v>
       </c>
       <c r="Y6" t="b">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>452</v>
+        <v>1251</v>
       </c>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" s="3" t="n">
-        <v>0.5986632950171411</v>
+        <v>0.7261744121077349</v>
       </c>
       <c r="AD6" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="AH6" s="3" t="n">
@@ -1370,53 +1370,35 @@
         </is>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="AL6" s="3" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>5/6</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="AM6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
         <is>
           <t>3/6</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AP6" s="3" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>1/6</t>
-        </is>
-      </c>
-      <c r="AR6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>0/6</t>
-        </is>
-      </c>
-      <c r="AT6" s="3" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" s="3" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1426,7 +1408,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1457,32 +1439,32 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>36865</v>
+        <v>39364</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>37460</v>
+        <v>39881</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>39275</v>
+        <v>40582</v>
       </c>
       <c r="M7" t="n">
-        <v>1656</v>
+        <v>840</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.4206842640084347</v>
+        <v>-0.4132656805387509</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.4206842640084347</v>
+        <v>-0.4132656805387509</v>
       </c>
       <c r="P7" t="n">
-        <v>1655</v>
+        <v>839</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.2271324373454977</v>
+        <v>0.1875151787644888</v>
       </c>
       <c r="R7" t="b">
         <v>0</v>
@@ -1492,32 +1474,32 @@
       </c>
       <c r="T7" s="3" t="inlineStr"/>
       <c r="U7" t="n">
-        <v>405</v>
+        <v>355</v>
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" s="3" t="n">
-        <v>-0.4206842640084347</v>
+        <v>-0.4132656805387509</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>-0.4206842640084347</v>
+        <v>-0.4132656805387509</v>
       </c>
       <c r="Y7" t="b">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1251</v>
+        <v>485</v>
       </c>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" s="3" t="n">
-        <v>0.7261744121077349</v>
+        <v>0.7043489136926906</v>
       </c>
       <c r="AD7" s="3" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="AF7" s="3" t="n">
@@ -1537,11 +1519,11 @@
         </is>
       </c>
       <c r="AJ7" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="AL7" s="3" t="n">
@@ -1553,11 +1535,11 @@
         </is>
       </c>
       <c r="AN7" s="3" t="n">
-        <v>0.5</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="AP7" s="3" t="inlineStr"/>
@@ -1575,7 +1557,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1593,49 +1575,45 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>39364</v>
+        <v>41901</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>39881</v>
+        <v>42508</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>40582</v>
+        <v>43025</v>
       </c>
       <c r="M8" t="n">
-        <v>840</v>
+        <v>775</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.4132656805387509</v>
+        <v>-0.2030988214540164</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.4132656805387509</v>
+        <v>-0.2030988214540164</v>
       </c>
       <c r="P8" t="n">
-        <v>839</v>
+        <v>774</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.1875151787644888</v>
+        <v>0.1298809830448981</v>
       </c>
       <c r="R8" t="b">
         <v>0</v>
@@ -1645,32 +1623,32 @@
       </c>
       <c r="T8" s="3" t="inlineStr"/>
       <c r="U8" t="n">
-        <v>355</v>
+        <v>418</v>
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" s="3" t="n">
-        <v>-0.4132656805387509</v>
+        <v>-0.2030988214540164</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>-0.4132656805387509</v>
+        <v>-0.2030988214540164</v>
       </c>
       <c r="Y8" t="b">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>485</v>
+        <v>357</v>
       </c>
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" s="3" t="n">
-        <v>0.7043489136926906</v>
+        <v>0.2548607367159226</v>
       </c>
       <c r="AD8" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="AF8" s="3" t="n">
@@ -1690,53 +1668,35 @@
         </is>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="AL8" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="AN8" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>1/6</t>
-        </is>
-      </c>
-      <c r="AP8" s="3" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AR8" s="3" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>1/6</t>
-        </is>
-      </c>
-      <c r="AT8" s="3" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
+          <t>3/6</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" s="3" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1746,7 +1706,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1777,32 +1737,32 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>41901</v>
+        <v>39364</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>42508</v>
+        <v>39881</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>43025</v>
+        <v>40575</v>
       </c>
       <c r="M9" t="n">
-        <v>775</v>
+        <v>835</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.2030988214540164</v>
+        <v>-0.4046464598524494</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.2030988214540164</v>
+        <v>-0.4046464598524494</v>
       </c>
       <c r="P9" t="n">
-        <v>774</v>
+        <v>834</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.1298809830448981</v>
+        <v>0.1813145997371987</v>
       </c>
       <c r="R9" t="b">
         <v>0</v>
@@ -1812,40 +1772,40 @@
       </c>
       <c r="T9" s="3" t="inlineStr"/>
       <c r="U9" t="n">
-        <v>418</v>
+        <v>355</v>
       </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" s="3" t="n">
-        <v>-0.2030988214540164</v>
+        <v>-0.4046464598524494</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>-0.2030988214540164</v>
+        <v>-0.4046464598524494</v>
       </c>
       <c r="Y9" t="b">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>357</v>
+        <v>480</v>
       </c>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" s="3" t="n">
-        <v>0.2548607367159226</v>
+        <v>0.6796742314695283</v>
       </c>
       <c r="AD9" s="3" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="AH9" s="3" t="n">
@@ -1857,11 +1817,11 @@
         </is>
       </c>
       <c r="AJ9" s="3" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AL9" s="3" t="n">
@@ -1873,11 +1833,11 @@
         </is>
       </c>
       <c r="AN9" s="3" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AP9" s="3" t="inlineStr"/>
@@ -1886,177 +1846,6 @@
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" s="3" t="inlineStr"/>
       <c r="AU9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>hrp</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>39364</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>40575</v>
-      </c>
-      <c r="M10" t="n">
-        <v>835</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.4046464598524494</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.4046464598524494</v>
-      </c>
-      <c r="P10" t="n">
-        <v>834</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.1813145997371987</v>
-      </c>
-      <c r="R10" t="b">
-        <v>0</v>
-      </c>
-      <c r="S10" t="b">
-        <v>0</v>
-      </c>
-      <c r="T10" s="3" t="inlineStr"/>
-      <c r="U10" t="n">
-        <v>355</v>
-      </c>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" s="3" t="n">
-        <v>-0.4046464598524494</v>
-      </c>
-      <c r="X10" s="3" t="n">
-        <v>-0.4046464598524494</v>
-      </c>
-      <c r="Y10" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>480</v>
-      </c>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" s="3" t="n">
-        <v>0.6796742314695283</v>
-      </c>
-      <c r="AD10" s="3" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>5/6</t>
-        </is>
-      </c>
-      <c r="AF10" s="3" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>5/6</t>
-        </is>
-      </c>
-      <c r="AH10" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>3/6</t>
-        </is>
-      </c>
-      <c r="AJ10" s="3" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AL10" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>6/6</t>
-        </is>
-      </c>
-      <c r="AN10" s="3" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AP10" s="3" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AR10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>0/6</t>
-        </is>
-      </c>
-      <c r="AT10" s="3" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2069,7 +1858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AO9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2543,12 +2332,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2558,7 +2347,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2569,41 +2358,45 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
         <v>36608</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>37460</v>
+        <v>36650</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>37783</v>
+        <v>36691</v>
       </c>
       <c r="M4" t="n">
-        <v>806</v>
+        <v>57</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.2185683866529438</v>
+        <v>-0.05147169288927356</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.3180206894883698</v>
+        <v>-0.08024052864543563</v>
       </c>
       <c r="P4" t="n">
-        <v>292</v>
+        <v>44</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.1252308092487745</v>
+        <v>0.04874849339161143</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.08167972914679614</v>
+        <v>0.008523962479549958</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>39364</v>
@@ -2616,38 +2409,38 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>583</v>
+        <v>29</v>
       </c>
       <c r="X4" t="n">
-        <v>-55</v>
+        <v>-609</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.2185683866529438</v>
+        <v>-0.05147169288927356</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.3180206894883698</v>
+        <v>-0.08024052864543563</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>223</v>
+        <v>28</v>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="b">
         <v>1</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.2797025138473266</v>
+        <v>0.05426479368450199</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.0239148133976206</v>
+        <v>-0.09707058006486677</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.08445325250127234</v>
+        <v>0.2515499462649425</v>
       </c>
       <c r="AH4" t="n">
-        <v>-157</v>
+        <v>-352</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -2667,7 +2460,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2698,35 +2491,35 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
         <v>36608</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>36650</v>
+        <v>37460</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>36691</v>
+        <v>37984</v>
       </c>
       <c r="M5" t="n">
-        <v>57</v>
+        <v>945</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.05147169288927356</v>
+        <v>-0.2743669899047804</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.08024052864543563</v>
+        <v>-0.3180206894883701</v>
       </c>
       <c r="P5" t="n">
-        <v>44</v>
+        <v>750</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.04874849339161143</v>
+        <v>0.1248682744061106</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.008523962479549958</v>
+        <v>0.08817876518329669</v>
       </c>
       <c r="S5" s="2" t="n">
         <v>39364</v>
@@ -2739,38 +2532,38 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>29</v>
+        <v>583</v>
       </c>
       <c r="X5" t="n">
-        <v>-609</v>
+        <v>-55</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.05147169288927356</v>
+        <v>-0.2743669899047804</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.08024052864543563</v>
+        <v>-0.3180206894883701</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>28</v>
+        <v>362</v>
       </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="b">
         <v>1</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.05426479368450199</v>
+        <v>0.3781070955809702</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.09707058006486677</v>
+        <v>-0.01741577736112004</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.2515499462649425</v>
+        <v>0.02865464924943573</v>
       </c>
       <c r="AH5" t="n">
-        <v>-352</v>
+        <v>-18</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -2790,7 +2583,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2808,24 +2601,20 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
@@ -2835,25 +2624,25 @@
         <v>37460</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>37984</v>
+        <v>39010</v>
       </c>
       <c r="M6" t="n">
-        <v>945</v>
+        <v>1654</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.2743669899047804</v>
+        <v>-0.3707291891787622</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.3180206894883701</v>
+        <v>-0.4206842640084347</v>
       </c>
       <c r="P6" t="n">
-        <v>750</v>
+        <v>1497</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.1248682744061106</v>
+        <v>0.2269390861406406</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.08817876518329669</v>
+        <v>0.2119701149283922</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>39364</v>
@@ -2872,48 +2661,40 @@
         <v>-55</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.2743669899047804</v>
+        <v>-0.3707291891787622</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.3180206894883701</v>
+        <v>-0.4206842640084347</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>362</v>
+        <v>1071</v>
       </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="b">
         <v>1</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.3781070955809702</v>
+        <v>0.5891409275681123</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.01741577736112004</v>
+        <v>0.1063755723839755</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.02865464924943573</v>
+        <v>-0.06770755002454609</v>
       </c>
       <c r="AH6" t="n">
-        <v>-18</v>
+        <v>691</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
-      <c r="AJ6" s="3" t="n">
-        <v>0.006499036036500552</v>
-      </c>
-      <c r="AK6" s="3" t="n">
-        <v>-0.05579860325183661</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>139</v>
-      </c>
-      <c r="AM6" t="b">
-        <v>0</v>
-      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
       <c r="AN6" s="3" t="inlineStr"/>
       <c r="AO6" s="3" t="inlineStr"/>
     </row>
@@ -2925,7 +2706,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2956,7 +2737,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
@@ -2966,25 +2747,25 @@
         <v>37460</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>39010</v>
+        <v>38012</v>
       </c>
       <c r="M7" t="n">
-        <v>1654</v>
+        <v>963</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.3707291891787622</v>
+        <v>-0.304433402926603</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.4206842640084347</v>
+        <v>-0.3514343814258261</v>
       </c>
       <c r="P7" t="n">
-        <v>1497</v>
+        <v>813</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.2269390861406406</v>
+        <v>0.1530038467936797</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.2119701149283922</v>
+        <v>0.1090704742282111</v>
       </c>
       <c r="S7" s="2" t="n">
         <v>39364</v>
@@ -3003,32 +2784,32 @@
         <v>-55</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.3707291891787622</v>
+        <v>-0.304433402926603</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.4206842640084347</v>
+        <v>-0.3514343814258261</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1071</v>
+        <v>380</v>
       </c>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="b">
         <v>1</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.5891409275681123</v>
+        <v>0.4376768582728232</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.1063755723839755</v>
+        <v>0.003475931683794342</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>-0.06770755002454609</v>
+        <v>-0.001411763772386943</v>
       </c>
       <c r="AH7" t="n">
-        <v>691</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -3048,7 +2829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3066,52 +2847,48 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
         <v>36608</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>37460</v>
+        <v>36811</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>38012</v>
+        <v>36825</v>
       </c>
       <c r="M8" t="n">
-        <v>963</v>
+        <v>151</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.304433402926603</v>
+        <v>-0.03090597893805125</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.3514343814258261</v>
+        <v>-0.05950659223009558</v>
       </c>
       <c r="P8" t="n">
-        <v>813</v>
+        <v>29</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.1530038467936797</v>
+        <v>0.01570784462048723</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.1090704742282111</v>
+        <v>0.004446361051362849</v>
       </c>
       <c r="S8" s="2" t="n">
         <v>39364</v>
@@ -3124,56 +2901,52 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>583</v>
+        <v>141</v>
       </c>
       <c r="X8" t="n">
-        <v>-55</v>
+        <v>-497</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.304433402926603</v>
+        <v>-0.03090597893805125</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.3514343814258261</v>
+        <v>-0.05950659223009558</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>380</v>
+        <v>10</v>
       </c>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="b">
         <v>1</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.4376768582728232</v>
+        <v>0.03189162069556883</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.003475931683794342</v>
+        <v>-0.1011481814930539</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>-0.001411763772386943</v>
+        <v>0.2721156602161648</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>-370</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
-      <c r="AJ8" s="3" t="n">
-        <v>0.02739074508141494</v>
-      </c>
-      <c r="AK8" s="3" t="n">
-        <v>-0.08586501627365928</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>157</v>
-      </c>
-      <c r="AM8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN8" s="3" t="inlineStr"/>
-      <c r="AO8" s="3" t="inlineStr"/>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" s="3" t="n">
+        <v>-0.001279829547892186</v>
+      </c>
+      <c r="AO8" s="3" t="n">
+        <v>0.009113158068361216</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3183,7 +2956,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3214,35 +2987,35 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
         <v>36608</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>36811</v>
+        <v>37460</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>36825</v>
+        <v>37971</v>
       </c>
       <c r="M9" t="n">
-        <v>151</v>
+        <v>937</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.03090597893805125</v>
+        <v>-0.2634509672518215</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.05950659223009558</v>
+        <v>-0.3272689968646514</v>
       </c>
       <c r="P9" t="n">
-        <v>29</v>
+        <v>546</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.01570784462048723</v>
+        <v>0.1304437500997335</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.004446361051362849</v>
+        <v>0.09172569889366439</v>
       </c>
       <c r="S9" s="2" t="n">
         <v>39364</v>
@@ -3255,38 +3028,38 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>141</v>
+        <v>583</v>
       </c>
       <c r="X9" t="n">
-        <v>-497</v>
+        <v>-55</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.03090597893805125</v>
+        <v>-0.2634509672518215</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.05950659223009558</v>
+        <v>-0.3272689968646514</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>10</v>
+        <v>354</v>
       </c>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="b">
         <v>1</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.03189162069556883</v>
+        <v>0.3576828636497493</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.1011481814930539</v>
+        <v>-0.01386884365075235</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.2721156602161648</v>
+        <v>0.03957067190239461</v>
       </c>
       <c r="AH9" t="n">
-        <v>-370</v>
+        <v>-26</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -3299,145 +3072,6 @@
         <v>-0.001279829547892186</v>
       </c>
       <c r="AO9" s="3" t="n">
-        <v>0.009113158068361216</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>hrp</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>36608</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>37460</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>37971</v>
-      </c>
-      <c r="M10" t="n">
-        <v>937</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.2634509672518215</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.3272689968646514</v>
-      </c>
-      <c r="P10" t="n">
-        <v>546</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.1304437500997335</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.09172569889366439</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>39364</v>
-      </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" t="b">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3" t="inlineStr"/>
-      <c r="W10" t="n">
-        <v>583</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-55</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>-0.2634509672518215</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>-0.3272689968646514</v>
-      </c>
-      <c r="AA10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>354</v>
-      </c>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE10" s="3" t="n">
-        <v>0.3576828636497493</v>
-      </c>
-      <c r="AF10" s="3" t="n">
-        <v>-0.01386884365075235</v>
-      </c>
-      <c r="AG10" s="3" t="n">
-        <v>0.03957067190239461</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>-26</v>
-      </c>
-      <c r="AI10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="3" t="n">
-        <v>0.01004596974686825</v>
-      </c>
-      <c r="AK10" s="3" t="n">
-        <v>-0.04488258059887773</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>131</v>
-      </c>
-      <c r="AM10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN10" s="3" t="n">
-        <v>-0.001279829547892186</v>
-      </c>
-      <c r="AO10" s="3" t="n">
         <v>-0.06347578376244911</v>
       </c>
     </row>
@@ -3452,7 +3086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AO9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3930,12 +3564,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3945,7 +3579,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3956,41 +3590,45 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
         <v>39364</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>39881</v>
+        <v>40765</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>40533</v>
+        <v>40784</v>
       </c>
       <c r="M4" t="n">
-        <v>807</v>
+        <v>980</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.3743492138682257</v>
+        <v>-0.06650268752313993</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.3744774130256878</v>
+        <v>-0.124381038500744</v>
       </c>
       <c r="P4" t="n">
-        <v>805</v>
+        <v>20</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.1546755474705558</v>
+        <v>0.01447996037147796</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.08370501759350023</v>
+        <v>0.008634277982305786</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>43364</v>
@@ -4003,40 +3641,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>355</v>
+        <v>967</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>612</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.3743492138682257</v>
+        <v>-0.06650268752313993</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.3744774130256878</v>
+        <v>-0.124381038500744</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>452</v>
+        <v>13</v>
       </c>
       <c r="AC4" t="n">
-        <v>-408</v>
+        <v>-847</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.5983357204467421</v>
+        <v>0.07124036313150972</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.03911159975450017</v>
+        <v>-0.1141823393656946</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.08144826705662001</v>
+        <v>0.3892947934017058</v>
       </c>
       <c r="AH4" t="n">
-        <v>-260</v>
+        <v>-699</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -4045,8 +3683,12 @@
       <c r="AK4" s="3" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
-      <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AN4" s="3" t="n">
+        <v>0.1213750437267103</v>
+      </c>
+      <c r="AO4" s="3" t="n">
+        <v>-0.0871167904264869</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4056,7 +3698,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4087,35 +3729,35 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
         <v>39364</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>40765</v>
+        <v>39881</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>40784</v>
+        <v>40533</v>
       </c>
       <c r="M5" t="n">
-        <v>980</v>
+        <v>807</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.06650268752313993</v>
+        <v>-0.3743492138682257</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.124381038500744</v>
+        <v>-0.3744774130256878</v>
       </c>
       <c r="P5" t="n">
-        <v>20</v>
+        <v>805</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.01447996037147796</v>
+        <v>0.1546755474705559</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.008634277982305786</v>
+        <v>0.08370501759350027</v>
       </c>
       <c r="S5" s="2" t="n">
         <v>43364</v>
@@ -4128,40 +3770,40 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>967</v>
+        <v>355</v>
       </c>
       <c r="X5" t="n">
-        <v>612</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.06650268752313993</v>
+        <v>-0.3743492138682257</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.124381038500744</v>
+        <v>-0.3744774130256878</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>13</v>
+        <v>452</v>
       </c>
       <c r="AC5" t="n">
-        <v>-847</v>
+        <v>-408</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.07124036313150972</v>
+        <v>0.5983357204467421</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.1141823393656946</v>
+        <v>-0.03911159975450013</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.3892947934017058</v>
+        <v>0.08144826705662001</v>
       </c>
       <c r="AH5" t="n">
-        <v>-699</v>
+        <v>-260</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -4174,7 +3816,7 @@
         <v>0.1213750437267103</v>
       </c>
       <c r="AO5" s="3" t="n">
-        <v>-0.0871167904264869</v>
+        <v>0.01477161720148734</v>
       </c>
     </row>
     <row r="6">
@@ -4185,7 +3827,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4203,52 +3845,48 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
         <v>39364</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>39881</v>
+        <v>40004</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>40533</v>
+        <v>40486</v>
       </c>
       <c r="M6" t="n">
-        <v>807</v>
+        <v>775</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.3743492138682257</v>
+        <v>-0.2686838800141741</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.3744774130256878</v>
+        <v>-0.2686838800141741</v>
       </c>
       <c r="P6" t="n">
-        <v>805</v>
+        <v>774</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.1546755474705559</v>
+        <v>0.1462285789728066</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.08370501759350027</v>
+        <v>0.07755097637482335</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>43364</v>
@@ -4261,62 +3899,50 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>355</v>
+        <v>441</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.3743492138682257</v>
+        <v>-0.2686838800141741</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.3744774130256878</v>
+        <v>-0.2686838800141741</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>452</v>
+        <v>334</v>
       </c>
       <c r="AC6" t="n">
-        <v>-408</v>
+        <v>-526</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.5983357204467421</v>
+        <v>0.3673977267441906</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.03911159975450013</v>
+        <v>-0.04526564097317705</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.08144826705662001</v>
+        <v>0.1871136009106716</v>
       </c>
       <c r="AH6" t="n">
-        <v>-260</v>
+        <v>-378</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
-      <c r="AJ6" s="3" t="n">
-        <v>4.163336342344337e-17</v>
-      </c>
-      <c r="AK6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN6" s="3" t="n">
-        <v>0.1213750437267103</v>
-      </c>
-      <c r="AO6" s="3" t="n">
-        <v>0.01477161720148734</v>
-      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4326,7 +3952,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4357,35 +3983,35 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
         <v>39364</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>40004</v>
+        <v>39881</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>40486</v>
+        <v>40582</v>
       </c>
       <c r="M7" t="n">
-        <v>775</v>
+        <v>840</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.2686838800141741</v>
+        <v>-0.4132656805387505</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.2686838800141741</v>
+        <v>-0.4132656805387505</v>
       </c>
       <c r="P7" t="n">
-        <v>774</v>
+        <v>839</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.1462285789728066</v>
+        <v>0.1875151787644882</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.07755097637482335</v>
+        <v>0.1035281791970789</v>
       </c>
       <c r="S7" s="2" t="n">
         <v>43364</v>
@@ -4398,40 +4024,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>441</v>
+        <v>355</v>
       </c>
       <c r="X7" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.2686838800141741</v>
+        <v>-0.4132656805387505</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.2686838800141741</v>
+        <v>-0.4132656805387505</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>334</v>
+        <v>485</v>
       </c>
       <c r="AC7" t="n">
-        <v>-526</v>
+        <v>-375</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.3673977267441906</v>
+        <v>0.7043489136926893</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.04526564097317705</v>
+        <v>-0.01928843815092152</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.1871136009106716</v>
+        <v>0.04253180038609528</v>
       </c>
       <c r="AH7" t="n">
-        <v>-378</v>
+        <v>-227</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -4451,7 +4077,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4469,52 +4095,48 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
         <v>39364</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>39881</v>
+        <v>40420</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>40582</v>
+        <v>40659</v>
       </c>
       <c r="M8" t="n">
-        <v>840</v>
+        <v>893</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.4132656805387505</v>
+        <v>-0.1975522224118726</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.4132656805387505</v>
+        <v>-0.1975522224118726</v>
       </c>
       <c r="P8" t="n">
-        <v>839</v>
+        <v>892</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.1875151787644882</v>
+        <v>0.1139108380713977</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.1035281791970789</v>
+        <v>0.06484223207808255</v>
       </c>
       <c r="S8" s="2" t="n">
         <v>43364</v>
@@ -4527,56 +4149,48 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>355</v>
+        <v>728</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>373</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.4132656805387505</v>
+        <v>-0.1975522224118726</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.4132656805387505</v>
+        <v>-0.1975522224118726</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>485</v>
+        <v>165</v>
       </c>
       <c r="AC8" t="n">
-        <v>-375</v>
+        <v>-695</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.7043489136926893</v>
+        <v>0.2461870141950475</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.01928843815092152</v>
+        <v>-0.05797438526991784</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.04253180038609528</v>
+        <v>0.2582452585129731</v>
       </c>
       <c r="AH8" t="n">
-        <v>-227</v>
+        <v>-547</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
-      <c r="AJ8" s="3" t="n">
-        <v>0.01982316160357865</v>
-      </c>
-      <c r="AK8" s="3" t="n">
-        <v>-0.03891646667052473</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>33</v>
-      </c>
-      <c r="AM8" t="b">
-        <v>0</v>
-      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
       <c r="AN8" s="3" t="inlineStr"/>
       <c r="AO8" s="3" t="inlineStr"/>
     </row>
@@ -4588,7 +4202,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4619,35 +4233,35 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
         <v>39364</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>40420</v>
+        <v>39881</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>40659</v>
+        <v>40575</v>
       </c>
       <c r="M9" t="n">
-        <v>893</v>
+        <v>835</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.1975522224118726</v>
+        <v>-0.4046464598524491</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.1975522224118726</v>
+        <v>-0.4046464598524491</v>
       </c>
       <c r="P9" t="n">
-        <v>892</v>
+        <v>834</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.1139108380713977</v>
+        <v>0.1813145997371984</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.06484223207808255</v>
+        <v>0.09980678450430396</v>
       </c>
       <c r="S9" s="2" t="n">
         <v>43364</v>
@@ -4660,40 +4274,40 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>728</v>
+        <v>355</v>
       </c>
       <c r="X9" t="n">
-        <v>373</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.1975522224118726</v>
+        <v>-0.4046464598524491</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.1975522224118726</v>
+        <v>-0.4046464598524491</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>165</v>
+        <v>480</v>
       </c>
       <c r="AC9" t="n">
-        <v>-695</v>
+        <v>-380</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.2461870141950475</v>
+        <v>0.6796742314695274</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.05797438526991784</v>
+        <v>-0.02300983284369644</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.2582452585129731</v>
+        <v>0.05115102107239666</v>
       </c>
       <c r="AH9" t="n">
-        <v>-547</v>
+        <v>-232</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -4704,143 +4318,6 @@
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" s="3" t="inlineStr"/>
       <c r="AO9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>hrp</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>39364</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>40575</v>
-      </c>
-      <c r="M10" t="n">
-        <v>835</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.4046464598524491</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.4046464598524491</v>
-      </c>
-      <c r="P10" t="n">
-        <v>834</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.1813145997371984</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.09980678450430396</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>43364</v>
-      </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" t="b">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3" t="inlineStr"/>
-      <c r="W10" t="n">
-        <v>355</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>-0.4046464598524491</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>-0.4046464598524491</v>
-      </c>
-      <c r="AA10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>480</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>-380</v>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="3" t="n">
-        <v>0.6796742314695274</v>
-      </c>
-      <c r="AF10" s="3" t="n">
-        <v>-0.02300983284369644</v>
-      </c>
-      <c r="AG10" s="3" t="n">
-        <v>0.05115102107239666</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>-232</v>
-      </c>
-      <c r="AI10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="3" t="n">
-        <v>0.01610176691080373</v>
-      </c>
-      <c r="AK10" s="3" t="n">
-        <v>-0.03029724598422334</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>28</v>
-      </c>
-      <c r="AM10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4853,7 +4330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AO9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5331,12 +4808,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -5346,7 +4823,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -5357,13 +4834,17 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
@@ -5373,25 +4854,25 @@
         <v>43458</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>43563</v>
+        <v>43545</v>
       </c>
       <c r="M4" t="n">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.1360620360985055</v>
+        <v>-0.1425767900867722</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.143729669862375</v>
+        <v>-0.1452798889626855</v>
       </c>
       <c r="P4" t="n">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.04849898132196487</v>
+        <v>0.04899572133157781</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.03006079347508416</v>
+        <v>0.02899795472484739</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>43880</v>
@@ -5410,34 +4891,34 @@
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.1360620360985055</v>
+        <v>-0.1425767900867722</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.143729669862375</v>
+        <v>-0.1452798889626855</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="AC4" t="n">
-        <v>-5</v>
+        <v>-17</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.1574905164302043</v>
+        <v>0.1662852001652733</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>0.001062838750236765</v>
+        <v>0</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.006514753988266619</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -5457,7 +4938,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5488,7 +4969,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
@@ -5582,7 +5063,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5600,52 +5081,48 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
         <v>43364</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>43458</v>
+        <v>43384</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>43545</v>
+        <v>43543</v>
       </c>
       <c r="M6" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.1425767900867722</v>
+        <v>-0.05636256056298983</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.1452798889626855</v>
+        <v>-0.05636256056298983</v>
       </c>
       <c r="P6" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.04899572133157781</v>
+        <v>0.02477631782469418</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.02899795472484739</v>
+        <v>0.01454504428038811</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>43880</v>
@@ -5658,56 +5135,48 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>64</v>
+        <v>14</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.1425767900867722</v>
+        <v>-0.05636256056298983</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.1452798889626855</v>
+        <v>-0.05636256056298983</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="AC6" t="n">
-        <v>-17</v>
+        <v>31</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.1662852001652733</v>
+        <v>0.05972904232860521</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0</v>
+        <v>-0.01445291044445929</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0</v>
+        <v>0.08621422952378233</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
-      <c r="AJ6" s="3" t="n">
-        <v>-0.001062838750236765</v>
-      </c>
-      <c r="AK6" s="3" t="n">
-        <v>-0.006514753988266619</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>-12</v>
-      </c>
-      <c r="AM6" t="b">
-        <v>0</v>
-      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
       <c r="AN6" s="3" t="inlineStr"/>
       <c r="AO6" s="3" t="inlineStr"/>
     </row>
@@ -5719,7 +5188,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -5750,35 +5219,35 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
         <v>43364</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>43384</v>
+        <v>43458</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>43543</v>
+        <v>43563</v>
       </c>
       <c r="M7" t="n">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.05636256056298983</v>
+        <v>-0.1418475533411727</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.05636256056298983</v>
+        <v>-0.1437296698623749</v>
       </c>
       <c r="P7" t="n">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.02477631782469418</v>
+        <v>0.04883325330106329</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.01454504428038811</v>
+        <v>0.03026798300060177</v>
       </c>
       <c r="S7" s="2" t="n">
         <v>43880</v>
@@ -5791,40 +5260,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="X7" t="n">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.05636256056298983</v>
+        <v>-0.1418475533411727</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.05636256056298983</v>
+        <v>-0.1437296698623749</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>107</v>
+        <v>71</v>
       </c>
       <c r="AC7" t="n">
-        <v>31</v>
+        <v>-5</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.05972904232860521</v>
+        <v>0.1652941198192104</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.01445291044445929</v>
+        <v>0.001270028275754374</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.08621422952378233</v>
+        <v>0.0007292367455994375</v>
       </c>
       <c r="AH7" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -5844,7 +5313,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5862,52 +5331,48 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
         <v>43364</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>43458</v>
+        <v>43384</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>43563</v>
+        <v>43536</v>
       </c>
       <c r="M8" t="n">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.1418475533411727</v>
+        <v>-0.05636256056298983</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.1437296698623749</v>
+        <v>-0.05636256056298983</v>
       </c>
       <c r="P8" t="n">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.04883325330106329</v>
+        <v>0.02427652230153897</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.03026798300060177</v>
+        <v>0.01395654025265442</v>
       </c>
       <c r="S8" s="2" t="n">
         <v>43880</v>
@@ -5920,56 +5385,48 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>64</v>
+        <v>14</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.1418475533411727</v>
+        <v>-0.05636256056298983</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.1437296698623749</v>
+        <v>-0.05636256056298983</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="AC8" t="n">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.1652941198192104</v>
+        <v>0.05972904232860521</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.001270028275754374</v>
+        <v>-0.01504141447219298</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.0007292367455994375</v>
+        <v>0.08621422952378233</v>
       </c>
       <c r="AH8" t="n">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
-      <c r="AJ8" s="3" t="n">
-        <v>0.0002071895255176086</v>
-      </c>
-      <c r="AK8" s="3" t="n">
-        <v>-0.005785517242667182</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="b">
-        <v>0</v>
-      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
       <c r="AN8" s="3" t="inlineStr"/>
       <c r="AO8" s="3" t="inlineStr"/>
     </row>
@@ -5981,7 +5438,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -6012,35 +5469,35 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
         <v>43364</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>43384</v>
+        <v>43458</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>43536</v>
+        <v>43560</v>
       </c>
       <c r="M9" t="n">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.05636256056298983</v>
+        <v>-0.1418475533411727</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.05636256056298983</v>
+        <v>-0.1437296698623749</v>
       </c>
       <c r="P9" t="n">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.02427652230153897</v>
+        <v>0.04865097833827546</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.01395654025265442</v>
+        <v>0.03004393621625156</v>
       </c>
       <c r="S9" s="2" t="n">
         <v>43880</v>
@@ -6053,40 +5510,40 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="X9" t="n">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.05636256056298983</v>
+        <v>-0.1418475533411727</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.05636256056298983</v>
+        <v>-0.1437296698623749</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="AC9" t="n">
-        <v>26</v>
+        <v>-6</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.05972904232860521</v>
+        <v>0.1652941198192104</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.01504141447219298</v>
+        <v>0.001045981491404169</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.08621422952378233</v>
+        <v>0.0007292367455994375</v>
       </c>
       <c r="AH9" t="n">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -6097,143 +5554,6 @@
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" s="3" t="inlineStr"/>
       <c r="AO9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>hrp</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>43364</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>43458</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>43560</v>
-      </c>
-      <c r="M10" t="n">
-        <v>134</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.1418475533411727</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.1437296698623749</v>
-      </c>
-      <c r="P10" t="n">
-        <v>130</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.04865097833827546</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.03004393621625156</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>43880</v>
-      </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" t="b">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3" t="inlineStr"/>
-      <c r="W10" t="n">
-        <v>64</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>-0.1418475533411727</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>-0.1437296698623749</v>
-      </c>
-      <c r="AA10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>70</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>-6</v>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="3" t="n">
-        <v>0.1652941198192104</v>
-      </c>
-      <c r="AF10" s="3" t="n">
-        <v>0.001045981491404169</v>
-      </c>
-      <c r="AG10" s="3" t="n">
-        <v>0.0007292367455994375</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AI10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="3" t="n">
-        <v>-1.685725883259631e-05</v>
-      </c>
-      <c r="AK10" s="3" t="n">
-        <v>-0.005785517242667182</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AM10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6246,7 +5566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AO9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6724,12 +6044,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -6739,7 +6059,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -6750,13 +6070,17 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
@@ -6765,26 +6089,24 @@
       <c r="K4" s="2" t="n">
         <v>43913</v>
       </c>
-      <c r="L4" s="2" t="n">
-        <v>44055</v>
-      </c>
+      <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>122</v>
+        <v>473</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.2893340076613283</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.2893340076613283</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="P4" t="n">
-        <v>121</v>
+        <v>473</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.1193940004707371</v>
+        <v>0.2240027313817356</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.0608199262236669</v>
+        <v>0.2240027313817356</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>44564</v>
@@ -6793,9 +6115,11 @@
         <v>0</v>
       </c>
       <c r="U4" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>-0.2267861662107663</v>
+      </c>
       <c r="W4" t="n">
         <v>23</v>
       </c>
@@ -6803,37 +6127,33 @@
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.2893340076613283</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.2893340076613283</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>99</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>44</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.4071307910896131</v>
+        <v>0.4203549201436105</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.0004471880537548975</v>
+        <v>0.1627356171043138</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.006616612977285663</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>-4</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ4" s="3" t="inlineStr"/>
       <c r="AK4" s="3" t="inlineStr"/>
@@ -6850,7 +6170,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -6881,7 +6201,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
@@ -6890,9 +6210,11 @@
       <c r="K5" s="2" t="n">
         <v>43913</v>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="n">
+        <v>44069</v>
+      </c>
       <c r="M5" t="n">
-        <v>473</v>
+        <v>132</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>-0.295950620638614</v>
@@ -6901,13 +6223,13 @@
         <v>-0.295950620638614</v>
       </c>
       <c r="P5" t="n">
-        <v>473</v>
+        <v>131</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.2240027313817356</v>
+        <v>0.1234494991627859</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.2240027313817356</v>
+        <v>0.06539220501861497</v>
       </c>
       <c r="S5" s="2" t="n">
         <v>44564</v>
@@ -6916,11 +6238,9 @@
         <v>0</v>
       </c>
       <c r="U5" t="b">
-        <v>1</v>
-      </c>
-      <c r="V5" s="3" t="n">
-        <v>-0.2267861662107663</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
         <v>23</v>
       </c>
@@ -6937,24 +6257,28 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>450</v>
-      </c>
-      <c r="AC5" t="inlineStr"/>
+        <v>109</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>54</v>
+      </c>
       <c r="AD5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
         <v>0.4203549201436105</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>0.1627356171043138</v>
+        <v>0.004125090741193167</v>
       </c>
       <c r="AG5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr"/>
+      <c r="AH5" t="n">
+        <v>6</v>
+      </c>
       <c r="AI5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ5" s="3" t="inlineStr"/>
       <c r="AK5" s="3" t="inlineStr"/>
@@ -6971,7 +6295,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -6989,52 +6313,48 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
         <v>43880</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>43913</v>
+        <v>44008</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>44069</v>
+        <v>44048</v>
       </c>
       <c r="M6" t="n">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.03618165451728028</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.07538615706116925</v>
       </c>
       <c r="P6" t="n">
-        <v>131</v>
+        <v>34</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.1234494991627859</v>
+        <v>0.02824530815121295</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.06539220501861497</v>
+        <v>0.01409282795134045</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>44564</v>
@@ -7047,58 +6367,54 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.03618165451728028</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.07538615706116925</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>109</v>
+        <v>27</v>
       </c>
       <c r="AC6" t="n">
-        <v>54</v>
+        <v>-28</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.4203549201436105</v>
+        <v>0.03753991059296458</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.004125090741193167</v>
+        <v>-0.04717428632608135</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0</v>
+        <v>0.2597689661213337</v>
       </c>
       <c r="AH6" t="n">
-        <v>6</v>
+        <v>-76</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
-      <c r="AJ6" s="3" t="n">
-        <v>0.004572278794948065</v>
-      </c>
-      <c r="AK6" s="3" t="n">
-        <v>-0.006616612977285663</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AM6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN6" s="3" t="inlineStr"/>
-      <c r="AO6" s="3" t="inlineStr"/>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" s="3" t="n">
+        <v>0.02027751002917078</v>
+      </c>
+      <c r="AO6" s="3" t="n">
+        <v>-0.0192674312508917</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7108,7 +6424,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -7139,35 +6455,35 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
         <v>43880</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>44008</v>
+        <v>43913</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>44048</v>
+        <v>44067</v>
       </c>
       <c r="M7" t="n">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.03618165451728028</v>
+        <v>-0.2893340076613283</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.07538615706116925</v>
+        <v>-0.2893340076613283</v>
       </c>
       <c r="P7" t="n">
-        <v>34</v>
+        <v>129</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.02824530815121295</v>
+        <v>0.1161546000586732</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.01409282795134045</v>
+        <v>0.0610636683717568</v>
       </c>
       <c r="S7" s="2" t="n">
         <v>44564</v>
@@ -7180,40 +6496,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>90</v>
+        <v>23</v>
       </c>
       <c r="X7" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.03618165451728028</v>
+        <v>-0.2893340076613283</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.07538615706116925</v>
+        <v>-0.2893340076613283</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>27</v>
+        <v>107</v>
       </c>
       <c r="AC7" t="n">
-        <v>-28</v>
+        <v>52</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.03753991059296458</v>
+        <v>0.4071307910896131</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.04717428632608135</v>
+        <v>-0.0002034459056649979</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.2597689661213337</v>
+        <v>0.006616612977285663</v>
       </c>
       <c r="AH7" t="n">
-        <v>-76</v>
+        <v>4</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -7226,7 +6542,7 @@
         <v>0.02027751002917078</v>
       </c>
       <c r="AO7" s="3" t="n">
-        <v>-0.0192674312508917</v>
+        <v>-0.004450505083797629</v>
       </c>
     </row>
     <row r="8">
@@ -7237,7 +6553,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -7255,52 +6571,48 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
         <v>43880</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>43913</v>
+        <v>43889</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>44067</v>
+        <v>44075</v>
       </c>
       <c r="M8" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.2893340076613283</v>
+        <v>-0.1195800593377413</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.2893340076613283</v>
+        <v>-0.1195800593377413</v>
       </c>
       <c r="P8" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.1161546000586732</v>
+        <v>0.07004471576271205</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.0610636683717568</v>
+        <v>0.03765706691064431</v>
       </c>
       <c r="S8" s="2" t="n">
         <v>44564</v>
@@ -7313,62 +6625,50 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.2893340076613283</v>
+        <v>-0.1195800593377413</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.2893340076613283</v>
+        <v>-0.1195800593377413</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="AC8" t="n">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.4071307910896131</v>
+        <v>0.1358216162707448</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.0002034459056649979</v>
+        <v>-0.02361004736677749</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.006616612977285663</v>
+        <v>0.1763705613008727</v>
       </c>
       <c r="AH8" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
-      <c r="AJ8" s="3" t="n">
-        <v>0.0002437421480898996</v>
-      </c>
-      <c r="AK8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AM8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN8" s="3" t="n">
-        <v>0.02027751002917078</v>
-      </c>
-      <c r="AO8" s="3" t="n">
-        <v>-0.004450505083797629</v>
-      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" s="3" t="inlineStr"/>
+      <c r="AO8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7378,7 +6678,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -7409,35 +6709,35 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
         <v>43880</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>43889</v>
+        <v>43913</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>44075</v>
+        <v>44067</v>
       </c>
       <c r="M9" t="n">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.1195800593377413</v>
+        <v>-0.2918967743785572</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.1195800593377413</v>
+        <v>-0.2918967743785572</v>
       </c>
       <c r="P9" t="n">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.07004471576271205</v>
+        <v>0.1183655577125906</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.03765706691064431</v>
+        <v>0.06222599155908312</v>
       </c>
       <c r="S9" s="2" t="n">
         <v>44564</v>
@@ -7450,40 +6750,40 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="X9" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.1195800593377413</v>
+        <v>-0.2918967743785572</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.1195800593377413</v>
+        <v>-0.2918967743785572</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="AC9" t="n">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.1358216162707448</v>
+        <v>0.412223477900957</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.02361004736677749</v>
+        <v>0.0009588772816613231</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.1763705613008727</v>
+        <v>0.004053846260056782</v>
       </c>
       <c r="AH9" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -7494,143 +6794,6 @@
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" s="3" t="inlineStr"/>
       <c r="AO9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>hrp</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>43880</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>44067</v>
-      </c>
-      <c r="M10" t="n">
-        <v>130</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.2918967743785572</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.2918967743785572</v>
-      </c>
-      <c r="P10" t="n">
-        <v>129</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.1183655577125906</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.06222599155908312</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>44564</v>
-      </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" t="b">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3" t="inlineStr"/>
-      <c r="W10" t="n">
-        <v>23</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>-0.2918967743785572</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>-0.2918967743785572</v>
-      </c>
-      <c r="AA10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>107</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>52</v>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="3" t="n">
-        <v>0.412223477900957</v>
-      </c>
-      <c r="AF10" s="3" t="n">
-        <v>0.0009588772816613231</v>
-      </c>
-      <c r="AG10" s="3" t="n">
-        <v>0.004053846260056782</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="3" t="n">
-        <v>0.001406065335416221</v>
-      </c>
-      <c r="AK10" s="3" t="n">
-        <v>-0.002562766717228881</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>8</v>
-      </c>
-      <c r="AM10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7643,7 +6806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AO9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8121,12 +7284,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -8136,7 +7299,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -8147,41 +7310,45 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
         <v>44564</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>44729</v>
+        <v>44846</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>45317</v>
+        <v>45301</v>
       </c>
       <c r="M4" t="n">
-        <v>518</v>
+        <v>507</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.2223141762956242</v>
+        <v>-0.2032134999970446</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.2223141762956242</v>
+        <v>-0.2173480216895393</v>
       </c>
       <c r="P4" t="n">
-        <v>517</v>
+        <v>476</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.1212946577391739</v>
+        <v>0.1161029160879204</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.0986257965760659</v>
+        <v>0.09339855465440339</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>45707</v>
@@ -8194,40 +7361,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>115</v>
+        <v>195</v>
       </c>
       <c r="X4" t="n">
-        <v>-80</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.2223141762956242</v>
+        <v>-0.2032134999970446</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.2223141762956242</v>
+        <v>-0.2173480216895393</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>403</v>
+        <v>312</v>
       </c>
       <c r="AC4" t="n">
-        <v>183</v>
+        <v>92</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.2858663094007141</v>
+        <v>0.2550413441948263</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>0.005239693611383614</v>
+        <v>1.245168972109634e-05</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.01544570038530024</v>
+        <v>0.03454637668387983</v>
       </c>
       <c r="AH4" t="n">
-        <v>205</v>
+        <v>114</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -8236,8 +7403,12 @@
       <c r="AK4" s="3" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
-      <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AN4" s="3" t="n">
+        <v>0.672706785284984</v>
+      </c>
+      <c r="AO4" s="3" t="n">
+        <v>-0.4013611977680653</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8247,7 +7418,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -8278,7 +7449,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
@@ -8288,25 +7459,25 @@
         <v>44846</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>45301</v>
+        <v>45317</v>
       </c>
       <c r="M5" t="n">
-        <v>507</v>
+        <v>518</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.2032134999970446</v>
+        <v>-0.2400831038360258</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.2173480216895393</v>
+        <v>-0.2400831038360258</v>
       </c>
       <c r="P5" t="n">
-        <v>476</v>
+        <v>517</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.1161029160879204</v>
+        <v>0.1332952539449779</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.09339855465440339</v>
+        <v>0.1083835912081281</v>
       </c>
       <c r="S5" s="2" t="n">
         <v>45707</v>
@@ -8325,34 +7496,34 @@
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.2032134999970446</v>
+        <v>-0.2400831038360258</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.2173480216895393</v>
+        <v>-0.2400831038360258</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="AC5" t="n">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.2550413441948263</v>
+        <v>0.3159333672510169</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>1.245168972109634e-05</v>
+        <v>0.01499748824344581</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.03454637668387983</v>
+        <v>-0.002323227155101359</v>
       </c>
       <c r="AH5" t="n">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -8365,7 +7536,7 @@
         <v>0.672706785284984</v>
       </c>
       <c r="AO5" s="3" t="n">
-        <v>-0.4013611977680653</v>
+        <v>-0.04869290891591871</v>
       </c>
     </row>
     <row r="6">
@@ -8376,7 +7547,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -8394,52 +7565,48 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
         <v>44564</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>44846</v>
+        <v>44586</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>45317</v>
+        <v>45019</v>
       </c>
       <c r="M6" t="n">
-        <v>518</v>
+        <v>313</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.2400831038360258</v>
+        <v>-0.08708938851250325</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.2400831038360258</v>
+        <v>-0.08708938851250325</v>
       </c>
       <c r="P6" t="n">
-        <v>517</v>
+        <v>312</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.1332952539449779</v>
+        <v>0.03986676943861766</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.1083835912081281</v>
+        <v>0.02521395887576482</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>45707</v>
@@ -8452,61 +7619,53 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>195</v>
+        <v>15</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-180</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.2400831038360258</v>
+        <v>-0.08708938851250325</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.2400831038360258</v>
+        <v>-0.08708938851250325</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>323</v>
+        <v>298</v>
       </c>
       <c r="AC6" t="n">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.3159333672510169</v>
+        <v>0.09539749830555677</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.01499748824344581</v>
+        <v>-0.06817214408891747</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>-0.002323227155101359</v>
+        <v>0.1506704881684212</v>
       </c>
       <c r="AH6" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
-      <c r="AJ6" s="3" t="n">
-        <v>0.009757794632062194</v>
-      </c>
-      <c r="AK6" s="3" t="n">
-        <v>-0.0177689275404016</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>-80</v>
-      </c>
-      <c r="AM6" t="b">
-        <v>0</v>
-      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
       <c r="AN6" s="3" t="n">
-        <v>0.672706785284984</v>
+        <v>0.06336097314022338</v>
       </c>
       <c r="AO6" s="3" t="n">
-        <v>-0.04869290891591871</v>
+        <v>-0.06047836550494423</v>
       </c>
     </row>
     <row r="7">
@@ -8517,7 +7676,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -8548,35 +7707,35 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
         <v>44564</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>44586</v>
+        <v>44729</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>45019</v>
+        <v>45152</v>
       </c>
       <c r="M7" t="n">
-        <v>313</v>
+        <v>404</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.08708938851250325</v>
+        <v>-0.2205813583428692</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.08708938851250325</v>
+        <v>-0.2205813583428692</v>
       </c>
       <c r="P7" t="n">
-        <v>312</v>
+        <v>403</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.03986676943861766</v>
+        <v>0.1274788262297419</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.02521395887576482</v>
+        <v>0.09156526133515572</v>
       </c>
       <c r="S7" s="2" t="n">
         <v>45707</v>
@@ -8589,40 +7748,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>15</v>
+        <v>115</v>
       </c>
       <c r="X7" t="n">
-        <v>-180</v>
+        <v>-80</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.08708938851250325</v>
+        <v>-0.2205813583428692</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.08708938851250325</v>
+        <v>-0.2205813583428692</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="AC7" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.09539749830555677</v>
+        <v>0.2830075476176559</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.06817214408891747</v>
+        <v>-0.001820841629526573</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.1506704881684212</v>
+        <v>0.01717851833805528</v>
       </c>
       <c r="AH7" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -8635,7 +7794,7 @@
         <v>0.06336097314022338</v>
       </c>
       <c r="AO7" s="3" t="n">
-        <v>-0.06047836550494423</v>
+        <v>-0.004593434956671416</v>
       </c>
     </row>
     <row r="8">
@@ -8646,7 +7805,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -8664,52 +7823,48 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
         <v>44564</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>44729</v>
+        <v>44995</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>45152</v>
+        <v>45019</v>
       </c>
       <c r="M8" t="n">
-        <v>404</v>
+        <v>313</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.2205813583428692</v>
+        <v>-0.06972871986006512</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.2205813583428692</v>
+        <v>-0.1129718168111257</v>
       </c>
       <c r="P8" t="n">
-        <v>403</v>
+        <v>151</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.1274788262297419</v>
+        <v>0.05148947965219722</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.09156526133515572</v>
+        <v>0.03256480624756752</v>
       </c>
       <c r="S8" s="2" t="n">
         <v>45707</v>
@@ -8722,61 +7877,53 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>115</v>
+        <v>297</v>
       </c>
       <c r="X8" t="n">
-        <v>-80</v>
+        <v>102</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.2205813583428692</v>
+        <v>-0.06972871986006512</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.2205813583428692</v>
+        <v>-0.1129718168111257</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>289</v>
+        <v>16</v>
       </c>
       <c r="AC8" t="n">
-        <v>69</v>
+        <v>-204</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.2830075476176559</v>
+        <v>0.07495525375090195</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.001820841629526573</v>
+        <v>-0.06082129671711477</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.01717851833805528</v>
+        <v>0.1680311568208593</v>
       </c>
       <c r="AH8" t="n">
-        <v>91</v>
+        <v>-182</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
-      <c r="AJ8" s="3" t="n">
-        <v>-0.007060535240910187</v>
-      </c>
-      <c r="AK8" s="3" t="n">
-        <v>0.001732817952755039</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>-114</v>
-      </c>
-      <c r="AM8" t="b">
-        <v>0</v>
-      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
       <c r="AN8" s="3" t="n">
         <v>0.06336097314022338</v>
       </c>
       <c r="AO8" s="3" t="n">
-        <v>-0.004593434956671416</v>
+        <v>-0.05953790568057138</v>
       </c>
     </row>
     <row r="9">
@@ -8787,7 +7934,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -8818,35 +7965,35 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
         <v>44564</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>44995</v>
+        <v>44846</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>45019</v>
+        <v>45293</v>
       </c>
       <c r="M9" t="n">
-        <v>313</v>
+        <v>501</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.06972871986006512</v>
+        <v>-0.2275727539629055</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.1129718168111257</v>
+        <v>-0.2275727539629055</v>
       </c>
       <c r="P9" t="n">
-        <v>151</v>
+        <v>500</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.05148947965219722</v>
+        <v>0.1214611782756227</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.03256480624756752</v>
+        <v>0.09713025301409862</v>
       </c>
       <c r="S9" s="2" t="n">
         <v>45707</v>
@@ -8859,40 +8006,40 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>297</v>
+        <v>195</v>
       </c>
       <c r="X9" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.06972871986006512</v>
+        <v>-0.2275727539629055</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.1129718168111257</v>
+        <v>-0.2275727539629055</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>16</v>
+        <v>306</v>
       </c>
       <c r="AC9" t="n">
-        <v>-204</v>
+        <v>86</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.07495525375090195</v>
+        <v>0.2946203090717709</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.06082129671711477</v>
+        <v>0.003744150049416334</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.1680311568208593</v>
+        <v>0.01018712271801892</v>
       </c>
       <c r="AH9" t="n">
-        <v>-182</v>
+        <v>108</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -8905,147 +8052,6 @@
         <v>0.06336097314022338</v>
       </c>
       <c r="AO9" s="3" t="n">
-        <v>-0.05953790568057138</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>hrp</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>44564</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>45293</v>
-      </c>
-      <c r="M10" t="n">
-        <v>501</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.2275727539629055</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.2275727539629055</v>
-      </c>
-      <c r="P10" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.1214611782756227</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.09713025301409862</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>45707</v>
-      </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" t="b">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3" t="inlineStr"/>
-      <c r="W10" t="n">
-        <v>195</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>-0.2275727539629055</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>-0.2275727539629055</v>
-      </c>
-      <c r="AA10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>306</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>86</v>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="3" t="n">
-        <v>0.2946203090717709</v>
-      </c>
-      <c r="AF10" s="3" t="n">
-        <v>0.003744150049416334</v>
-      </c>
-      <c r="AG10" s="3" t="n">
-        <v>0.01018712271801892</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>108</v>
-      </c>
-      <c r="AI10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="3" t="n">
-        <v>-0.00149554356196728</v>
-      </c>
-      <c r="AK10" s="3" t="n">
-        <v>-0.005258577667281328</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>-97</v>
-      </c>
-      <c r="AM10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN10" s="3" t="n">
-        <v>0.06336097314022338</v>
-      </c>
-      <c r="AO10" s="3" t="n">
         <v>-0.004259490730372684</v>
       </c>
     </row>
@@ -9060,7 +8066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AO9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9538,12 +8544,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -9553,7 +8559,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -9564,87 +8570,87 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
         <v>45707</v>
       </c>
-      <c r="K4" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>45917</v>
-      </c>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>145</v>
+        <v>88</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.1208786768201607</v>
+        <v>0</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.1208786768201607</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.06321320299387231</v>
+        <v>0</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.05173160794390522</v>
+        <v>0</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>46021</v>
       </c>
       <c r="T4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-34</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.1208786768201607</v>
+        <v>0</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.1208786768201607</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>56</v>
+        <v>-55</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.1374994254296262</v>
+        <v>0</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>0.00245474594780884</v>
+        <v>-0.04927686199609638</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.03048455108637682</v>
+        <v>0.1513632279065376</v>
       </c>
       <c r="AH4" t="n">
-        <v>9</v>
+        <v>-102</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -9653,8 +8659,12 @@
       <c r="AK4" s="3" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
-      <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AN4" s="3" t="n">
+        <v>0.1212838470749049</v>
+      </c>
+      <c r="AO4" s="3" t="n">
+        <v>-0.09017125420230654</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9664,7 +8674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -9695,77 +8705,81 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
         <v>45707</v>
       </c>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>45917</v>
+      </c>
       <c r="M5" t="n">
-        <v>88</v>
+        <v>145</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>0</v>
+        <v>-0.1208786768201607</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>0</v>
+        <v>-0.1208786768201607</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0</v>
+        <v>0.06321320299387231</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0</v>
+        <v>0.05173160794390522</v>
       </c>
       <c r="S5" s="2" t="n">
         <v>46021</v>
       </c>
       <c r="T5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="X5" t="n">
-        <v>-34</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0</v>
+        <v>-0.1208786768201607</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>0</v>
+        <v>-0.1208786768201607</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="AC5" t="n">
-        <v>-55</v>
+        <v>56</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0</v>
+        <v>0.1374994254296262</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.04927686199609638</v>
+        <v>0.00245474594780884</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.1513632279065376</v>
+        <v>0.03048455108637682</v>
       </c>
       <c r="AH5" t="n">
-        <v>-102</v>
+        <v>9</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -9778,7 +8792,7 @@
         <v>0.1212838470749049</v>
       </c>
       <c r="AO5" s="3" t="n">
-        <v>-0.09017125420230654</v>
+        <v>-0.03844538071637815</v>
       </c>
     </row>
     <row r="6">
@@ -9789,7 +8803,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -9807,52 +8821,48 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
         <v>45707</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>45755</v>
+        <v>45715</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>45917</v>
+        <v>45796</v>
       </c>
       <c r="M6" t="n">
-        <v>145</v>
+        <v>62</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.1208786768201607</v>
+        <v>-0.03420088913897812</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.1208786768201607</v>
+        <v>-0.03420088913897812</v>
       </c>
       <c r="P6" t="n">
-        <v>144</v>
+        <v>61</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.06321320299387231</v>
+        <v>0.02523214868067308</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.05173160794390522</v>
+        <v>0.01356426491137623</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>46021</v>
@@ -9865,62 +8875,50 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-28</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.1208786768201607</v>
+        <v>-0.03420088913897812</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.1208786768201607</v>
+        <v>-0.03420088913897812</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>111</v>
+        <v>56</v>
       </c>
       <c r="AC6" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.1374994254296262</v>
+        <v>0.03541201141559092</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.00245474594780884</v>
+        <v>-0.03571259708472015</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.03048455108637682</v>
+        <v>0.1171623387675594</v>
       </c>
       <c r="AH6" t="n">
-        <v>9</v>
+        <v>-46</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
-      <c r="AJ6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN6" s="3" t="n">
-        <v>0.1212838470749049</v>
-      </c>
-      <c r="AO6" s="3" t="n">
-        <v>-0.03844538071637815</v>
-      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9930,7 +8928,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -9961,35 +8959,35 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
         <v>45707</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>45715</v>
+        <v>45755</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>45796</v>
+        <v>45904</v>
       </c>
       <c r="M7" t="n">
-        <v>62</v>
+        <v>136</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.03420088913897812</v>
+        <v>-0.1306426784263617</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.03420088913897812</v>
+        <v>-0.1306426784263617</v>
       </c>
       <c r="P7" t="n">
-        <v>61</v>
+        <v>135</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.02523214868067308</v>
+        <v>0.05790825444661689</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.01356426491137623</v>
+        <v>0.04590632328515906</v>
       </c>
       <c r="S7" s="2" t="n">
         <v>46021</v>
@@ -10002,40 +9000,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="X7" t="n">
-        <v>-28</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.03420088913897812</v>
+        <v>-0.1306426784263617</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.03420088913897812</v>
+        <v>-0.1306426784263617</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>56</v>
+        <v>102</v>
       </c>
       <c r="AC7" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.03541201141559092</v>
+        <v>0.1502750079678206</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.03571259708472015</v>
+        <v>-0.003370538710937315</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.1171623387675594</v>
+        <v>0.02072054948017588</v>
       </c>
       <c r="AH7" t="n">
-        <v>-46</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -10055,7 +9053,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -10073,52 +9071,48 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
         <v>45707</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>45755</v>
+        <v>45729</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>45904</v>
+        <v>45909</v>
       </c>
       <c r="M8" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.1306426784263617</v>
+        <v>-0.1002080841471648</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.1306426784263617</v>
+        <v>-0.1002080841471648</v>
       </c>
       <c r="P8" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.05790825444661689</v>
+        <v>0.05846547124087626</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.04590632328515906</v>
+        <v>0.04685276498153609</v>
       </c>
       <c r="S8" s="2" t="n">
         <v>46021</v>
@@ -10131,56 +9125,48 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.1306426784263617</v>
+        <v>-0.1002080841471648</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.1306426784263617</v>
+        <v>-0.1002080841471648</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="AC8" t="n">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.1502750079678206</v>
+        <v>0.1113680645287707</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.003370538710937315</v>
+        <v>-0.002424097014560284</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.02072054948017588</v>
+        <v>0.0511551437593728</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
-      <c r="AJ8" s="3" t="n">
-        <v>-0.005825284658746155</v>
-      </c>
-      <c r="AK8" s="3" t="n">
-        <v>-0.009764001606200945</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>-9</v>
-      </c>
-      <c r="AM8" t="b">
-        <v>0</v>
-      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
       <c r="AN8" s="3" t="inlineStr"/>
       <c r="AO8" s="3" t="inlineStr"/>
     </row>
@@ -10192,7 +9178,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -10223,35 +9209,35 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
         <v>45707</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>45729</v>
+        <v>45755</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>45909</v>
+        <v>45989</v>
       </c>
       <c r="M9" t="n">
-        <v>139</v>
+        <v>196</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.1002080841471648</v>
+        <v>-0.1441736393992464</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.1002080841471648</v>
+        <v>-0.1441736393992464</v>
       </c>
       <c r="P9" t="n">
-        <v>138</v>
+        <v>195</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.05846547124087626</v>
+        <v>0.06951790341161816</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.04685276498153609</v>
+        <v>0.06608479270531507</v>
       </c>
       <c r="S9" s="2" t="n">
         <v>46021</v>
@@ -10264,40 +9250,40 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="X9" t="n">
-        <v>-18</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.1002080841471648</v>
+        <v>-0.1441736393992464</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.1002080841471648</v>
+        <v>-0.1441736393992464</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>123</v>
+        <v>162</v>
       </c>
       <c r="AC9" t="n">
-        <v>68</v>
+        <v>107</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.1113680645287707</v>
+        <v>0.1684613211703863</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.002424097014560284</v>
+        <v>0.0168079307092187</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.0511551437593728</v>
+        <v>0.007189588507291123</v>
       </c>
       <c r="AH9" t="n">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -10308,143 +9294,6 @@
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" s="3" t="inlineStr"/>
       <c r="AO9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>hrp</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>45707</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>45989</v>
-      </c>
-      <c r="M10" t="n">
-        <v>196</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.1441736393992464</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.1441736393992464</v>
-      </c>
-      <c r="P10" t="n">
-        <v>195</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.06951790341161816</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.06608479270531507</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>46021</v>
-      </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" t="b">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3" t="inlineStr"/>
-      <c r="W10" t="n">
-        <v>34</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>-0.1441736393992464</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>-0.1441736393992464</v>
-      </c>
-      <c r="AA10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>162</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>107</v>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="3" t="n">
-        <v>0.1684613211703863</v>
-      </c>
-      <c r="AF10" s="3" t="n">
-        <v>0.0168079307092187</v>
-      </c>
-      <c r="AG10" s="3" t="n">
-        <v>0.007189588507291123</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>60</v>
-      </c>
-      <c r="AI10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="3" t="n">
-        <v>0.01435318476140986</v>
-      </c>
-      <c r="AK10" s="3" t="n">
-        <v>-0.0232949625790857</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>51</v>
-      </c>
-      <c r="AM10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_variable_hrp_monthly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_variable_hrp_monthly.xlsx
@@ -14,7 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C4" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C5" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C6" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C7" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -917,27 +918,27 @@
         <v>0.837551214756322</v>
       </c>
       <c r="AD3" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AF3" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH3" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AJ3" s="3" t="inlineStr"/>
@@ -1048,51 +1049,51 @@
         <v>0.6231491074653142</v>
       </c>
       <c r="AD4" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH4" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AJ4" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AL4" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AN4" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AP4" s="3" t="inlineStr"/>
@@ -1197,51 +1198,51 @@
         <v>0.5986632950171411</v>
       </c>
       <c r="AD5" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH5" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AJ5" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AL5" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AN5" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AP5" s="3" t="inlineStr"/>
@@ -1346,11 +1347,11 @@
         <v>0.7261744121077349</v>
       </c>
       <c r="AD6" s="3" t="n">
-        <v>1</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AF6" s="3" t="n">
@@ -1358,39 +1359,39 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="AH6" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AL6" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AN6" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AP6" s="3" t="inlineStr"/>
@@ -1495,11 +1496,11 @@
         <v>0.7043489136926906</v>
       </c>
       <c r="AD7" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AF7" s="3" t="n">
@@ -1507,39 +1508,39 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="AH7" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AJ7" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AL7" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AN7" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AP7" s="3" t="inlineStr"/>
@@ -1648,7 +1649,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="AF8" s="3" t="n">
@@ -1656,15 +1657,15 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="AH8" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AJ8" s="3" t="n">
@@ -1672,7 +1673,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="AL8" s="3" t="n">
@@ -1680,15 +1681,15 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="AN8" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AP8" s="3" t="inlineStr"/>
@@ -1793,51 +1794,51 @@
         <v>0.6796742314695283</v>
       </c>
       <c r="AD9" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH9" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AJ9" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>1</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AN9" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AP9" s="3" t="inlineStr"/>
@@ -2142,66 +2143,68 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>37460</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+        <v>36038</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>36116</v>
+      </c>
       <c r="M2" t="n">
-        <v>1896</v>
+        <v>86</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>-0.4859401977791236</v>
+        <v>-0.1697286534192365</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>-0.486230944244141</v>
+        <v>-0.1697286534192365</v>
       </c>
       <c r="P2" t="n">
-        <v>1895</v>
+        <v>85</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>0.2657575172078731</v>
+        <v>0.0903200482301444</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>0.2657575172078731</v>
+        <v>0.04076898034342899</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
       </c>
       <c r="U2" t="b">
-        <v>1</v>
-      </c>
-      <c r="V2" s="3" t="n">
-        <v>-0.03939252582909292</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X2" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.4859401977791236</v>
+        <v>-0.1697286534192365</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.486230944244141</v>
+        <v>-0.1697286534192365</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1313</v>
-      </c>
-      <c r="AC2" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
       <c r="AD2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.9452989626493482</v>
+        <v>0.2044255219913533</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -2249,34 +2252,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>37460</v>
+        <v>36038</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>38012</v>
+        <v>36104</v>
       </c>
       <c r="M3" t="n">
-        <v>963</v>
+        <v>78</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>-0.3030216391542161</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>-0.3432461105733071</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="P3" t="n">
-        <v>829</v>
+        <v>77</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.1481278166620073</v>
+        <v>0.08381851803583454</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>0.1055945425444167</v>
+        <v>0.03605284870827317</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -2286,29 +2289,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X3" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.3030216391542161</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.3432461105733071</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>380</v>
-      </c>
-      <c r="AC3" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-8</v>
+      </c>
       <c r="AD3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.4347647734522189</v>
+        <v>0.1846197916504295</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -2372,34 +2377,34 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>36650</v>
+        <v>36038</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>36691</v>
+        <v>36482</v>
       </c>
       <c r="M4" t="n">
-        <v>57</v>
+        <v>339</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.05147169288927356</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.08024052864543563</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="P4" t="n">
-        <v>44</v>
+        <v>338</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.04874849339161143</v>
+        <v>0.0958649829367979</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.008523962479549958</v>
+        <v>0.08554320551505416</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -2409,38 +2414,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="X4" t="n">
-        <v>-609</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.05147169288927356</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.08024052864543563</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>28</v>
-      </c>
-      <c r="AC4" t="inlineStr"/>
+        <v>308</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>253</v>
+      </c>
       <c r="AD4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.05426479368450199</v>
+        <v>0.1846197916504295</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.09707058006486677</v>
+        <v>0.04949035680678099</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.2515499462649425</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>-352</v>
+        <v>261</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -2495,34 +2502,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>37460</v>
+        <v>36038</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>37984</v>
+        <v>36102</v>
       </c>
       <c r="M5" t="n">
-        <v>945</v>
+        <v>76</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.2743669899047804</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.3180206894883701</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="P5" t="n">
-        <v>750</v>
+        <v>75</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.1248682744061106</v>
+        <v>0.08323995922787236</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.08817876518329669</v>
+        <v>0.03534787283113147</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -2532,38 +2539,40 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X5" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.2743669899047804</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.3180206894883701</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>362</v>
-      </c>
-      <c r="AC5" t="inlineStr"/>
+        <v>45</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-10</v>
+      </c>
       <c r="AD5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.3781070955809702</v>
+        <v>0.1846197916504295</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.01741577736112004</v>
+        <v>-0.0007049758771417031</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.02865464924943573</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-18</v>
+        <v>-2</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -2618,34 +2627,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>37460</v>
+        <v>36038</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>39010</v>
+        <v>36158</v>
       </c>
       <c r="M6" t="n">
-        <v>1654</v>
+        <v>114</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.3707291891787622</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.4206842640084347</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="P6" t="n">
-        <v>1497</v>
+        <v>113</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.2269390861406406</v>
+        <v>0.08606474146807853</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.2119701149283922</v>
+        <v>0.04466427112753731</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -2655,38 +2664,40 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X6" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.3707291891787622</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.4206842640084347</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1071</v>
-      </c>
-      <c r="AC6" t="inlineStr"/>
+        <v>83</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>28</v>
+      </c>
       <c r="AD6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.5891409275681123</v>
+        <v>0.1846197916504295</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.1063755723839755</v>
+        <v>0.008611422419264138</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>-0.06770755002454609</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>691</v>
+        <v>36</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
@@ -2741,34 +2752,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>37460</v>
+        <v>36038</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>38012</v>
+        <v>36102</v>
       </c>
       <c r="M7" t="n">
-        <v>963</v>
+        <v>76</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.304433402926603</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.3514343814258261</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="P7" t="n">
-        <v>813</v>
+        <v>75</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.1530038467936797</v>
+        <v>0.08324014746752294</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.1090704742282111</v>
+        <v>0.03534795276715369</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -2778,38 +2789,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X7" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.304433402926603</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.3514343814258261</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>380</v>
-      </c>
-      <c r="AC7" t="inlineStr"/>
+        <v>45</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-10</v>
+      </c>
       <c r="AD7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.4376768582728232</v>
+        <v>0.1846197916504295</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.003475931683794342</v>
+        <v>-0.0007048959411194849</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>-0.001411763772386943</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -2864,75 +2877,73 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>36608</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>36811</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>36825</v>
-      </c>
+        <v>35993</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>151</v>
+        <v>90</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.03090597893805125</v>
+        <v>0</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.05950659223009558</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.01570784462048723</v>
+        <v>0</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.004446361051362849</v>
+        <v>0</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-497</v>
+        <v>-31</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.03090597893805125</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.05950659223009558</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC8" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-55</v>
+      </c>
       <c r="AD8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.03189162069556883</v>
+        <v>0</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.1011481814930539</v>
+        <v>-0.03605284870827317</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.2721156602161648</v>
+        <v>0.1558472962816319</v>
       </c>
       <c r="AH8" t="n">
-        <v>-370</v>
+        <v>-47</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
@@ -2942,10 +2953,10 @@
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr"/>
       <c r="AN8" s="3" t="n">
-        <v>-0.001279829547892186</v>
+        <v>0.08085941147512643</v>
       </c>
       <c r="AO8" s="3" t="n">
-        <v>0.009113158068361216</v>
+        <v>-0.0652324863726127</v>
       </c>
     </row>
     <row r="9">
@@ -2991,34 +3002,34 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>37460</v>
+        <v>36038</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>37971</v>
+        <v>36102</v>
       </c>
       <c r="M9" t="n">
-        <v>937</v>
+        <v>76</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.2634509672518215</v>
+        <v>-0.1581346033647496</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.3272689968646514</v>
+        <v>-0.1581346033647496</v>
       </c>
       <c r="P9" t="n">
-        <v>546</v>
+        <v>75</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.1304437500997335</v>
+        <v>0.08522521481650464</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.09172569889366439</v>
+        <v>0.03619091219269772</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -3028,38 +3039,40 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X9" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.2634509672518215</v>
+        <v>-0.1581346033647496</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.3272689968646514</v>
+        <v>-0.1581346033647496</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>354</v>
-      </c>
-      <c r="AC9" t="inlineStr"/>
+        <v>45</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-10</v>
+      </c>
       <c r="AD9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.3576828636497493</v>
+        <v>0.187838345650954</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.01386884365075235</v>
+        <v>0.0001380634844245499</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.03957067190239461</v>
+        <v>-0.002287307083117751</v>
       </c>
       <c r="AH9" t="n">
-        <v>-26</v>
+        <v>-2</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -3069,10 +3082,10 @@
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" s="3" t="n">
-        <v>-0.001279829547892186</v>
+        <v>0.08085941147512643</v>
       </c>
       <c r="AO9" s="3" t="n">
-        <v>-0.06347578376244911</v>
+        <v>-0.01981205682512033</v>
       </c>
     </row>
   </sheetData>
@@ -3370,68 +3383,66 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.4862309442441412</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.4862309442441412</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1895</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.2658275917027516</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.2658275917027516</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="K2" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>41124</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1215</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.503509252857314</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.5040024023286778</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1213</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.2352416489517779</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.1561727120528913</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="T2" t="b">
         <v>0</v>
       </c>
       <c r="U2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V2" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>-0.03993583465459927</v>
+      </c>
       <c r="W2" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.503509252857314</v>
+        <v>-0.4862309442441412</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.5040024023286778</v>
+        <v>-0.4862309442441412</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>860</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
+        <v>1313</v>
+      </c>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>1.014136226616547</v>
+        <v>0.9463998245842122</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -3479,34 +3490,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>38012</v>
+      </c>
+      <c r="M3" t="n">
+        <v>962</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.3013243461981798</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.343246110573307</v>
+      </c>
+      <c r="P3" t="n">
+        <v>813</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.1482043849238123</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.1056221565201652</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>40911</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1067</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.4557974809248457</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.4557974809248457</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1066</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.1974000942251041</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.1228166173480004</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -3516,31 +3527,29 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.4557974809248457</v>
+        <v>-0.3013243461981798</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.4557974809248457</v>
+        <v>-0.343246110573307</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>712</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>-148</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.8375512147563215</v>
+        <v>0.4312792989973724</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -3604,34 +3613,34 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>36650</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>36691</v>
+      </c>
+      <c r="M4" t="n">
+        <v>56</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.04916182144318404</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.08024052864543563</v>
+      </c>
+      <c r="P4" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.04915788741937696</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.008523372558492616</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>40765</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>40784</v>
-      </c>
-      <c r="M4" t="n">
-        <v>980</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-0.06650268752313993</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.124381038500744</v>
-      </c>
-      <c r="P4" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.01447996037147796</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.008634277982305786</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -3641,40 +3650,38 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>967</v>
+        <v>28</v>
       </c>
       <c r="X4" t="n">
-        <v>612</v>
+        <v>-609</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.06650268752313993</v>
+        <v>-0.04916182144318404</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.124381038500744</v>
+        <v>-0.08024052864543563</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>-847</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.07124036313150972</v>
+        <v>0.05170366793411896</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.1141823393656946</v>
+        <v>-0.09709878396167261</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.3892947934017058</v>
+        <v>0.2521625247549958</v>
       </c>
       <c r="AH4" t="n">
-        <v>-699</v>
+        <v>-352</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -3683,12 +3690,8 @@
       <c r="AK4" s="3" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
-      <c r="AN4" s="3" t="n">
-        <v>0.1213750437267103</v>
-      </c>
-      <c r="AO4" s="3" t="n">
-        <v>-0.0871167904264869</v>
-      </c>
+      <c r="AN4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3733,34 +3736,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>37984</v>
+      </c>
+      <c r="M5" t="n">
+        <v>944</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.2725999166843043</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.3180206894883703</v>
+      </c>
+      <c r="P5" t="n">
+        <v>733</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.124933936347554</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.08820174176426288</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>40533</v>
-      </c>
-      <c r="M5" t="n">
-        <v>807</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>-0.3743492138682257</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>-0.3744774130256878</v>
-      </c>
-      <c r="P5" t="n">
-        <v>805</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.1546755474705559</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0.08370501759350027</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -3770,40 +3773,38 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.3743492138682257</v>
+        <v>-0.2725999166843043</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.3744774130256878</v>
+        <v>-0.3180206894883703</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>452</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-408</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.5983357204467421</v>
+        <v>0.3747592596384051</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.03911159975450013</v>
+        <v>-0.01742041475590235</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.08144826705662001</v>
+        <v>0.02872442951387555</v>
       </c>
       <c r="AH5" t="n">
-        <v>-260</v>
+        <v>-18</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -3812,12 +3813,8 @@
       <c r="AK5" s="3" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
-      <c r="AN5" s="3" t="n">
-        <v>0.1213750437267103</v>
-      </c>
-      <c r="AO5" s="3" t="n">
-        <v>0.01477161720148734</v>
-      </c>
+      <c r="AN5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3862,34 +3859,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>39010</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1653</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.369196778741586</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.4206842640084347</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1487</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.227007556736974</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.2120258927658112</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>40004</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>40486</v>
-      </c>
-      <c r="M6" t="n">
-        <v>775</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.2686838800141741</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.2686838800141741</v>
-      </c>
-      <c r="P6" t="n">
-        <v>774</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.1462285789728066</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.07755097637482335</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -3899,40 +3896,38 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>441</v>
+        <v>582</v>
       </c>
       <c r="X6" t="n">
-        <v>86</v>
+        <v>-55</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.2686838800141741</v>
+        <v>-0.369196778741586</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.2686838800141741</v>
+        <v>-0.4206842640084347</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>334</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>-526</v>
-      </c>
+        <v>1071</v>
+      </c>
+      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.3673977267441906</v>
+        <v>0.5852804270800342</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.04526564097317705</v>
+        <v>0.1064037362456459</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.1871136009106716</v>
+        <v>-0.06787243254340614</v>
       </c>
       <c r="AH6" t="n">
-        <v>-378</v>
+        <v>691</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
@@ -3987,34 +3982,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>38012</v>
+      </c>
+      <c r="M7" t="n">
+        <v>962</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.3027395479204962</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.3514343814258259</v>
+      </c>
+      <c r="P7" t="n">
+        <v>797</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.1530829563269362</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.1090990120302126</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>40582</v>
-      </c>
-      <c r="M7" t="n">
-        <v>840</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-0.4132656805387505</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-0.4132656805387505</v>
-      </c>
-      <c r="P7" t="n">
-        <v>839</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.1875151787644882</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.1035281791970789</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -4024,40 +4019,38 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.4132656805387505</v>
+        <v>-0.3027395479204962</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.4132656805387505</v>
+        <v>-0.3514343814258259</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>485</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>-375</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.7043489136926893</v>
+        <v>0.434184309489529</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.01928843815092152</v>
+        <v>0.003476855510047422</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.04253180038609528</v>
+        <v>-0.00141520172231635</v>
       </c>
       <c r="AH7" t="n">
-        <v>-227</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -4112,34 +4105,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>36811</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>36825</v>
+      </c>
+      <c r="M8" t="n">
+        <v>150</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.0311262210553348</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.05950659223009569</v>
+      </c>
+      <c r="P8" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.0157597715211966</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.004447533460361834</v>
+      </c>
+      <c r="S8" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>40420</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>40659</v>
-      </c>
-      <c r="M8" t="n">
-        <v>893</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>-0.1975522224118726</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>-0.1975522224118726</v>
-      </c>
-      <c r="P8" t="n">
-        <v>892</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.1139108380713977</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.06484223207808255</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -4149,40 +4142,38 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>728</v>
+        <v>140</v>
       </c>
       <c r="X8" t="n">
-        <v>373</v>
+        <v>-497</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.1975522224118726</v>
+        <v>-0.0311262210553348</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.1975522224118726</v>
+        <v>-0.05950659223009569</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>165</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>-695</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.2461870141950475</v>
+        <v>0.03212618788098354</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.05797438526991784</v>
+        <v>-0.1011746230598034</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.2582452585129731</v>
+        <v>0.270198125142845</v>
       </c>
       <c r="AH8" t="n">
-        <v>-547</v>
+        <v>-370</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
@@ -4191,8 +4182,12 @@
       <c r="AK8" s="3" t="inlineStr"/>
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr"/>
-      <c r="AN8" s="3" t="inlineStr"/>
-      <c r="AO8" s="3" t="inlineStr"/>
+      <c r="AN8" s="3" t="n">
+        <v>-0.003706020729931647</v>
+      </c>
+      <c r="AO8" s="3" t="n">
+        <v>0.01180051457259657</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4237,34 +4232,34 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>37967</v>
+      </c>
+      <c r="M9" t="n">
+        <v>934</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.2618003498059318</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.3272689968646515</v>
+      </c>
+      <c r="P9" t="n">
+        <v>534</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.1305955347490613</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.09170963542055065</v>
+      </c>
+      <c r="S9" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>40575</v>
-      </c>
-      <c r="M9" t="n">
-        <v>835</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>-0.4046464598524491</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>-0.4046464598524491</v>
-      </c>
-      <c r="P9" t="n">
-        <v>834</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.1813145997371984</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>0.09980678450430396</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -4274,40 +4269,38 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.4046464598524491</v>
+        <v>-0.2618003498059318</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.4046464598524491</v>
+        <v>-0.3272689968646515</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>480</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>-380</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.6796742314695274</v>
+        <v>0.3546470791974856</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.02300983284369644</v>
+        <v>-0.01391252109961458</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.05115102107239666</v>
+        <v>0.03952399639224802</v>
       </c>
       <c r="AH9" t="n">
-        <v>-232</v>
+        <v>-28</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -4316,8 +4309,12 @@
       <c r="AK9" s="3" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
-      <c r="AN9" s="3" t="inlineStr"/>
-      <c r="AO9" s="3" t="inlineStr"/>
+      <c r="AN9" s="3" t="n">
+        <v>-0.003706020729931647</v>
+      </c>
+      <c r="AO9" s="3" t="n">
+        <v>-0.06329431637923577</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4614,34 +4611,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>43570</v>
+        <v>41124</v>
       </c>
       <c r="M2" t="n">
-        <v>140</v>
+        <v>1215</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>-0.1954368693665688</v>
+        <v>-0.503509252857314</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>-0.2022979914860074</v>
+        <v>-0.5040024023286778</v>
       </c>
       <c r="P2" t="n">
-        <v>132</v>
+        <v>1213</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>0.08269444253856417</v>
+        <v>0.2352416489517779</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>0.0521896337568788</v>
+        <v>0.1562010221613542</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -4651,22 +4648,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.1954368693665688</v>
+        <v>-0.503509252857314</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.2022979914860074</v>
+        <v>-0.5040024023286778</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>76</v>
+        <v>860</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -4675,7 +4672,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.2429105460160741</v>
+        <v>1.014136226616547</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -4723,34 +4720,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>43545</v>
+        <v>40911</v>
       </c>
       <c r="M3" t="n">
-        <v>123</v>
+        <v>1067</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>-0.1425767900867722</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>-0.1452798889626855</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="P3" t="n">
-        <v>119</v>
+        <v>1066</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.04899572133157781</v>
+        <v>0.1974000942251041</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>0.02899795472484739</v>
+        <v>0.1228388808517359</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -4760,31 +4757,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.1425767900867722</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.1452798889626855</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>59</v>
+        <v>712</v>
       </c>
       <c r="AC3" t="n">
-        <v>-17</v>
+        <v>-148</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.1662852001652733</v>
+        <v>0.8375512147563215</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -4848,34 +4845,34 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>43458</v>
+        <v>40765</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>43545</v>
+        <v>40784</v>
       </c>
       <c r="M4" t="n">
-        <v>123</v>
+        <v>980</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.1425767900867722</v>
+        <v>-0.06650268752313993</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.1452798889626855</v>
+        <v>-0.124381038500744</v>
       </c>
       <c r="P4" t="n">
-        <v>119</v>
+        <v>20</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.04899572133157781</v>
+        <v>0.01447996037147796</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.02899795472484739</v>
+        <v>0.008635843155523085</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -4885,40 +4882,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>64</v>
+        <v>967</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>612</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.1425767900867722</v>
+        <v>-0.06650268752313993</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.1452798889626855</v>
+        <v>-0.124381038500744</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="AC4" t="n">
-        <v>-17</v>
+        <v>-847</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.1662852001652733</v>
+        <v>0.07124036313150972</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>0</v>
+        <v>-0.1142030376962128</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0</v>
+        <v>0.3892947934017058</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>-699</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -4927,8 +4924,12 @@
       <c r="AK4" s="3" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
-      <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AN4" s="3" t="n">
+        <v>0.1213750437267103</v>
+      </c>
+      <c r="AO4" s="3" t="n">
+        <v>-0.0871167904264869</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4973,34 +4974,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>43545</v>
+        <v>40533</v>
       </c>
       <c r="M5" t="n">
-        <v>123</v>
+        <v>807</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.1425767900867722</v>
+        <v>-0.3743492138682257</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.1452798889626855</v>
+        <v>-0.3744774130256878</v>
       </c>
       <c r="P5" t="n">
-        <v>119</v>
+        <v>805</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.04899572133157781</v>
+        <v>0.1546755474705559</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.02899795472484739</v>
+        <v>0.08372019116701265</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -5010,40 +5011,40 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.1425767900867722</v>
+        <v>-0.3743492138682257</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.1452798889626855</v>
+        <v>-0.3744774130256878</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>59</v>
+        <v>452</v>
       </c>
       <c r="AC5" t="n">
-        <v>-17</v>
+        <v>-408</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.1662852001652733</v>
+        <v>0.5983357204467421</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>0</v>
+        <v>-0.03911868968472325</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0</v>
+        <v>0.08144826705662001</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>-260</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -5052,8 +5053,12 @@
       <c r="AK5" s="3" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
-      <c r="AN5" s="3" t="inlineStr"/>
-      <c r="AO5" s="3" t="inlineStr"/>
+      <c r="AN5" s="3" t="n">
+        <v>0.1213750437267103</v>
+      </c>
+      <c r="AO5" s="3" t="n">
+        <v>0.01477161720148734</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5098,34 +5103,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>43384</v>
+        <v>40004</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>43543</v>
+        <v>40486</v>
       </c>
       <c r="M6" t="n">
-        <v>121</v>
+        <v>775</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.05636256056298983</v>
+        <v>-0.2686838800141741</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.05636256056298983</v>
+        <v>-0.2686838800141741</v>
       </c>
       <c r="P6" t="n">
-        <v>120</v>
+        <v>774</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.02477631782469418</v>
+        <v>0.1462285789728066</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.01454504428038811</v>
+        <v>0.07756503437845098</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -5135,40 +5140,40 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>14</v>
+        <v>441</v>
       </c>
       <c r="X6" t="n">
-        <v>-50</v>
+        <v>86</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.05636256056298983</v>
+        <v>-0.2686838800141741</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.05636256056298983</v>
+        <v>-0.2686838800141741</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>107</v>
+        <v>334</v>
       </c>
       <c r="AC6" t="n">
-        <v>31</v>
+        <v>-526</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.05972904232860521</v>
+        <v>0.3673977267441906</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.01445291044445929</v>
+        <v>-0.04527384647328492</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.08621422952378233</v>
+        <v>0.1871136009106716</v>
       </c>
       <c r="AH6" t="n">
-        <v>48</v>
+        <v>-378</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
@@ -5223,34 +5228,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>43563</v>
+        <v>40582</v>
       </c>
       <c r="M7" t="n">
-        <v>135</v>
+        <v>840</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.1418475533411727</v>
+        <v>-0.4132656805387505</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.1437296698623749</v>
+        <v>-0.4132656805387505</v>
       </c>
       <c r="P7" t="n">
-        <v>131</v>
+        <v>839</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.04883325330106329</v>
+        <v>0.1875151787644882</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.03026798300060177</v>
+        <v>0.1035469462015287</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -5260,40 +5265,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.1418475533411727</v>
+        <v>-0.4132656805387505</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.1437296698623749</v>
+        <v>-0.4132656805387505</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>71</v>
+        <v>485</v>
       </c>
       <c r="AC7" t="n">
-        <v>-5</v>
+        <v>-375</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.1652941198192104</v>
+        <v>0.7043489136926893</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.001270028275754374</v>
+        <v>-0.01929193465020719</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.0007292367455994375</v>
+        <v>0.04253180038609528</v>
       </c>
       <c r="AH7" t="n">
-        <v>12</v>
+        <v>-227</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -5348,34 +5353,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>43384</v>
+        <v>40420</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>43536</v>
+        <v>40659</v>
       </c>
       <c r="M8" t="n">
-        <v>116</v>
+        <v>893</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.05636256056298983</v>
+        <v>-0.1975522224118726</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.05636256056298983</v>
+        <v>-0.1975522224118726</v>
       </c>
       <c r="P8" t="n">
-        <v>115</v>
+        <v>892</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.02427652230153897</v>
+        <v>0.1139108380713977</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.01395654025265442</v>
+        <v>0.06485398631221846</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -5385,40 +5390,40 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>14</v>
+        <v>728</v>
       </c>
       <c r="X8" t="n">
-        <v>-50</v>
+        <v>373</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.05636256056298983</v>
+        <v>-0.1975522224118726</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.05636256056298983</v>
+        <v>-0.1975522224118726</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>102</v>
+        <v>165</v>
       </c>
       <c r="AC8" t="n">
-        <v>26</v>
+        <v>-695</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.05972904232860521</v>
+        <v>0.2461870141950475</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.01504141447219298</v>
+        <v>-0.05798489453951744</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.08621422952378233</v>
+        <v>0.2582452585129731</v>
       </c>
       <c r="AH8" t="n">
-        <v>43</v>
+        <v>-547</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
@@ -5473,34 +5478,34 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>43560</v>
+        <v>40575</v>
       </c>
       <c r="M9" t="n">
-        <v>134</v>
+        <v>835</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.1418475533411727</v>
+        <v>-0.4046464598524491</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.1437296698623749</v>
+        <v>-0.4046464598524491</v>
       </c>
       <c r="P9" t="n">
-        <v>130</v>
+        <v>834</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.04865097833827546</v>
+        <v>0.1813145997371984</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.03004393621625156</v>
+        <v>0.09982487691531168</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -5510,40 +5515,40 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.1418475533411727</v>
+        <v>-0.4046464598524491</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.1437296698623749</v>
+        <v>-0.4046464598524491</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>70</v>
+        <v>480</v>
       </c>
       <c r="AC9" t="n">
-        <v>-6</v>
+        <v>-380</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.1652941198192104</v>
+        <v>0.6796742314695274</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.001045981491404169</v>
+        <v>-0.02301400393642422</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.0007292367455994375</v>
+        <v>0.05115102107239666</v>
       </c>
       <c r="AH9" t="n">
-        <v>11</v>
+        <v>-232</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -5850,34 +5855,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>43572</v>
+      </c>
+      <c r="M2" t="n">
+        <v>143</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.1989728318606706</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.2022979914860074</v>
+      </c>
+      <c r="P2" t="n">
+        <v>138</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.08183226369428352</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.05211846719049091</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>43992</v>
-      </c>
-      <c r="M2" t="n">
-        <v>78</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.2902196151348785</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.2902196151348785</v>
-      </c>
-      <c r="P2" t="n">
-        <v>77</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.1403286526425155</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.05728893254440421</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -5887,22 +5892,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.2902196151348785</v>
+        <v>-0.1989728318606706</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.2902196151348785</v>
+        <v>-0.2022979914860074</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -5911,7 +5916,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.4088864968986547</v>
+        <v>0.2483971078320051</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -5959,34 +5964,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>43545</v>
+      </c>
+      <c r="M3" t="n">
+        <v>124</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.1419538085967058</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.1452798889626854</v>
+      </c>
+      <c r="P3" t="n">
+        <v>118</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.04879934490473427</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.02895708373240715</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>44061</v>
-      </c>
-      <c r="M3" t="n">
-        <v>126</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.295950620638614</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.295950620638614</v>
-      </c>
-      <c r="P3" t="n">
-        <v>125</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.1183626651723915</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.0612671142774218</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -5996,31 +6001,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.1419538085967058</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.1452798889626854</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>103</v>
+        <v>59</v>
       </c>
       <c r="AC3" t="n">
-        <v>48</v>
+        <v>-19</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.4203549201436105</v>
+        <v>0.1654384228016292</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -6084,76 +6089,80 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>43545</v>
+      </c>
+      <c r="M4" t="n">
+        <v>124</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.1419538085967058</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.1452798889626854</v>
+      </c>
+      <c r="P4" t="n">
+        <v>118</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.04879934490473427</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.02895708373240715</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>43880</v>
       </c>
-      <c r="K4" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" t="n">
-        <v>473</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-0.295950620638614</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.295950620638614</v>
-      </c>
-      <c r="P4" t="n">
-        <v>473</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.2240027313817356</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.2240027313817356</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>44564</v>
-      </c>
       <c r="T4" t="b">
         <v>0</v>
       </c>
       <c r="U4" t="b">
-        <v>1</v>
-      </c>
-      <c r="V4" s="3" t="n">
-        <v>-0.2267861662107663</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.1419538085967058</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.1452798889626854</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>450</v>
-      </c>
-      <c r="AC4" t="inlineStr"/>
+        <v>59</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-19</v>
+      </c>
       <c r="AD4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.4203549201436105</v>
+        <v>0.1654384228016292</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>0.1627356171043138</v>
+        <v>0</v>
       </c>
       <c r="AG4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH4" t="inlineStr"/>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
       <c r="AI4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ4" s="3" t="inlineStr"/>
       <c r="AK4" s="3" t="inlineStr"/>
@@ -6205,34 +6214,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>43545</v>
+      </c>
+      <c r="M5" t="n">
+        <v>124</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.1419538085967058</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.1452798889626854</v>
+      </c>
+      <c r="P5" t="n">
+        <v>118</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.04879934490473427</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.02895708373240715</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>44069</v>
-      </c>
-      <c r="M5" t="n">
-        <v>132</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>-0.295950620638614</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>-0.295950620638614</v>
-      </c>
-      <c r="P5" t="n">
-        <v>131</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.1234494991627859</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0.06539220501861497</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -6242,40 +6251,40 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.1419538085967058</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.1452798889626854</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>109</v>
+        <v>59</v>
       </c>
       <c r="AC5" t="n">
-        <v>54</v>
+        <v>-19</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.4203549201436105</v>
+        <v>0.1654384228016292</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>0.004125090741193167</v>
+        <v>0</v>
       </c>
       <c r="AG5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -6330,34 +6339,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>43384</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>43542</v>
+      </c>
+      <c r="M6" t="n">
+        <v>121</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.05567693804740359</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.05636256056298983</v>
+      </c>
+      <c r="P6" t="n">
+        <v>119</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.0247763178246942</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.01452454385542824</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>44008</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>44048</v>
-      </c>
-      <c r="M6" t="n">
-        <v>117</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.03618165451728028</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.07538615706116925</v>
-      </c>
-      <c r="P6" t="n">
-        <v>34</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.02824530815121295</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.01409282795134045</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -6367,40 +6376,40 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="X6" t="n">
-        <v>67</v>
+        <v>-50</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.03618165451728028</v>
+        <v>-0.05567693804740359</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.07538615706116925</v>
+        <v>-0.05636256056298983</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>27</v>
+        <v>106</v>
       </c>
       <c r="AC6" t="n">
-        <v>-28</v>
+        <v>28</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.03753991059296458</v>
+        <v>0.05895962969736135</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.04717428632608135</v>
+        <v>-0.01443253987697891</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.2597689661213337</v>
+        <v>0.08627687054930222</v>
       </c>
       <c r="AH6" t="n">
-        <v>-76</v>
+        <v>47</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
@@ -6409,12 +6418,8 @@
       <c r="AK6" s="3" t="inlineStr"/>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr"/>
-      <c r="AN6" s="3" t="n">
-        <v>0.02027751002917078</v>
-      </c>
-      <c r="AO6" s="3" t="n">
-        <v>-0.0192674312508917</v>
-      </c>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6459,34 +6464,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>43560</v>
+      </c>
+      <c r="M7" t="n">
+        <v>135</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.1412240420065803</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.1437296698623748</v>
+      </c>
+      <c r="P7" t="n">
+        <v>130</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.04883325231991262</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.03022532136718326</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>44067</v>
-      </c>
-      <c r="M7" t="n">
-        <v>130</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-0.2893340076613283</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-0.2893340076613283</v>
-      </c>
-      <c r="P7" t="n">
-        <v>129</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.1161546000586732</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.0610636683717568</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -6496,40 +6501,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.2893340076613283</v>
+        <v>-0.1412240420065803</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.2893340076613283</v>
+        <v>-0.1437296698623748</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>107</v>
+        <v>70</v>
       </c>
       <c r="AC7" t="n">
-        <v>52</v>
+        <v>-8</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.4071307910896131</v>
+        <v>0.1644480620260476</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.0002034459056649979</v>
+        <v>0.001268237634776112</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.006616612977285663</v>
+        <v>0.0007297665901254691</v>
       </c>
       <c r="AH7" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -6538,12 +6543,8 @@
       <c r="AK7" s="3" t="inlineStr"/>
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
-      <c r="AN7" s="3" t="n">
-        <v>0.02027751002917078</v>
-      </c>
-      <c r="AO7" s="3" t="n">
-        <v>-0.004450505083797629</v>
-      </c>
+      <c r="AN7" s="3" t="inlineStr"/>
+      <c r="AO7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6588,34 +6589,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>43384</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>43536</v>
+      </c>
+      <c r="M8" t="n">
+        <v>117</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.05567693804740359</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.05636256056298983</v>
+      </c>
+      <c r="P8" t="n">
+        <v>115</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.02417343681547764</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.01393686929114798</v>
+      </c>
+      <c r="S8" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>43889</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>44075</v>
-      </c>
-      <c r="M8" t="n">
-        <v>136</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>-0.1195800593377413</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>-0.1195800593377413</v>
-      </c>
-      <c r="P8" t="n">
-        <v>135</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.07004471576271205</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.03765706691064431</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -6625,40 +6626,40 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="X8" t="n">
-        <v>-16</v>
+        <v>-50</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.1195800593377413</v>
+        <v>-0.05567693804740359</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.1195800593377413</v>
+        <v>-0.05636256056298983</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="AC8" t="n">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.1358216162707448</v>
+        <v>0.05895962969736135</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.02361004736677749</v>
+        <v>-0.01502021444125917</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.1763705613008727</v>
+        <v>0.08627687054930222</v>
       </c>
       <c r="AH8" t="n">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
@@ -6713,34 +6714,34 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>43913</v>
+        <v>43458</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>44067</v>
+        <v>43559</v>
       </c>
       <c r="M9" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.2918967743785572</v>
+        <v>-0.1412240420065803</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.2918967743785572</v>
+        <v>-0.1437296698623748</v>
       </c>
       <c r="P9" t="n">
         <v>129</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.1183655577125906</v>
+        <v>0.0486509783382754</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.06222599155908312</v>
+        <v>0.0300015909715051</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>44564</v>
+        <v>43880</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -6750,40 +6751,40 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.2918967743785572</v>
+        <v>-0.1412240420065803</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.2918967743785572</v>
+        <v>-0.1437296698623748</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>107</v>
+        <v>69</v>
       </c>
       <c r="AC9" t="n">
-        <v>52</v>
+        <v>-9</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.412223477900957</v>
+        <v>0.1644480620260476</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.0009588772816613231</v>
+        <v>0.00104450723909795</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.004053846260056782</v>
+        <v>0.0007297665901254691</v>
       </c>
       <c r="AH9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -7090,34 +7091,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>43992</v>
+      </c>
+      <c r="M2" t="n">
+        <v>78</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.2902196151348785</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.2902196151348785</v>
+      </c>
+      <c r="P2" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.1403286526425155</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.05728893254440421</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>44931</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>45250</v>
-      </c>
-      <c r="M2" t="n">
-        <v>473</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.3239608533428741</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.3239608533428741</v>
-      </c>
-      <c r="P2" t="n">
-        <v>472</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.1873955345996986</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.1456175032694572</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -7127,22 +7128,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>253</v>
+        <v>23</v>
       </c>
       <c r="X2" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.3239608533428741</v>
+        <v>-0.2902196151348785</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.3239608533428741</v>
+        <v>-0.2902196151348785</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>220</v>
+        <v>55</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -7151,7 +7152,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.4792042812088524</v>
+        <v>0.4088864968986547</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -7199,34 +7200,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>44061</v>
+      </c>
+      <c r="M3" t="n">
+        <v>126</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.295950620638614</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.295950620638614</v>
+      </c>
+      <c r="P3" t="n">
+        <v>125</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.1183626651723915</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.0612671142774218</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>45135</v>
-      </c>
-      <c r="M3" t="n">
-        <v>393</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.2377598766809245</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.2377598766809245</v>
-      </c>
-      <c r="P3" t="n">
-        <v>392</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.1318162553441144</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.09338610296468229</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -7236,31 +7237,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.2377598766809245</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.2377598766809245</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>198</v>
+        <v>103</v>
       </c>
       <c r="AC3" t="n">
-        <v>-22</v>
+        <v>48</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.3119225417387239</v>
+        <v>0.4203549201436105</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -7324,91 +7325,83 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>473</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.295950620638614</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.295950620638614</v>
+      </c>
+      <c r="P4" t="n">
+        <v>473</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.2240027313817356</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.2240027313817356</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>44564</v>
       </c>
-      <c r="K4" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>45301</v>
-      </c>
-      <c r="M4" t="n">
-        <v>507</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-0.2032134999970446</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.2173480216895393</v>
-      </c>
-      <c r="P4" t="n">
-        <v>476</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.1161029160879204</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.09339855465440339</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>45707</v>
-      </c>
       <c r="T4" t="b">
         <v>0</v>
       </c>
       <c r="U4" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>-0.2267861662107663</v>
+      </c>
       <c r="W4" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.2032134999970446</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.2173480216895393</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>312</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>92</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.2550413441948263</v>
+        <v>0.4203549201436105</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>1.245168972109634e-05</v>
+        <v>0.1627356171043138</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.03454637668387983</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>114</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ4" s="3" t="inlineStr"/>
       <c r="AK4" s="3" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
-      <c r="AN4" s="3" t="n">
-        <v>0.672706785284984</v>
-      </c>
-      <c r="AO4" s="3" t="n">
-        <v>-0.4013611977680653</v>
-      </c>
+      <c r="AN4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7453,34 +7446,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>44069</v>
+      </c>
+      <c r="M5" t="n">
+        <v>132</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.295950620638614</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.295950620638614</v>
+      </c>
+      <c r="P5" t="n">
+        <v>131</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.1234494991627859</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.06539220501861497</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>45317</v>
-      </c>
-      <c r="M5" t="n">
-        <v>518</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>-0.2400831038360258</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>-0.2400831038360258</v>
-      </c>
-      <c r="P5" t="n">
-        <v>517</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.1332952539449779</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0.1083835912081281</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -7490,40 +7483,40 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.2400831038360258</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.2400831038360258</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>323</v>
+        <v>109</v>
       </c>
       <c r="AC5" t="n">
-        <v>103</v>
+        <v>54</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.3159333672510169</v>
+        <v>0.4203549201436105</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>0.01499748824344581</v>
+        <v>0.004125090741193167</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>-0.002323227155101359</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>125</v>
+        <v>6</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -7532,12 +7525,8 @@
       <c r="AK5" s="3" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
-      <c r="AN5" s="3" t="n">
-        <v>0.672706785284984</v>
-      </c>
-      <c r="AO5" s="3" t="n">
-        <v>-0.04869290891591871</v>
-      </c>
+      <c r="AN5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7582,34 +7571,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>44008</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>44048</v>
+      </c>
+      <c r="M6" t="n">
+        <v>117</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.03618165451728028</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.07538615706116925</v>
+      </c>
+      <c r="P6" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.02824530815121295</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.01409282795134045</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>44586</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>45019</v>
-      </c>
-      <c r="M6" t="n">
-        <v>313</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.08708938851250325</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.08708938851250325</v>
-      </c>
-      <c r="P6" t="n">
-        <v>312</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.03986676943861766</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.02521395887576482</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -7619,40 +7608,40 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="X6" t="n">
-        <v>-180</v>
+        <v>67</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.08708938851250325</v>
+        <v>-0.03618165451728028</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.08708938851250325</v>
+        <v>-0.07538615706116925</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>298</v>
+        <v>27</v>
       </c>
       <c r="AC6" t="n">
-        <v>78</v>
+        <v>-28</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.09539749830555677</v>
+        <v>0.03753991059296458</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.06817214408891747</v>
+        <v>-0.04717428632608135</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.1506704881684212</v>
+        <v>0.2597689661213337</v>
       </c>
       <c r="AH6" t="n">
-        <v>100</v>
+        <v>-76</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
@@ -7662,10 +7651,10 @@
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" s="3" t="n">
-        <v>0.06336097314022338</v>
+        <v>0.02027751002917078</v>
       </c>
       <c r="AO6" s="3" t="n">
-        <v>-0.06047836550494423</v>
+        <v>-0.0192674312508917</v>
       </c>
     </row>
     <row r="7">
@@ -7711,34 +7700,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>44067</v>
+      </c>
+      <c r="M7" t="n">
+        <v>130</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.2893340076613283</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.2893340076613283</v>
+      </c>
+      <c r="P7" t="n">
+        <v>129</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.1161546000586732</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.0610636683717568</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>44729</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>45152</v>
-      </c>
-      <c r="M7" t="n">
-        <v>404</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-0.2205813583428692</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-0.2205813583428692</v>
-      </c>
-      <c r="P7" t="n">
-        <v>403</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.1274788262297419</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.09156526133515572</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -7748,40 +7737,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>115</v>
+        <v>23</v>
       </c>
       <c r="X7" t="n">
-        <v>-80</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.2205813583428692</v>
+        <v>-0.2893340076613283</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.2205813583428692</v>
+        <v>-0.2893340076613283</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>289</v>
+        <v>107</v>
       </c>
       <c r="AC7" t="n">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.2830075476176559</v>
+        <v>0.4071307910896131</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.001820841629526573</v>
+        <v>-0.0002034459056649979</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.01717851833805528</v>
+        <v>0.006616612977285663</v>
       </c>
       <c r="AH7" t="n">
-        <v>91</v>
+        <v>4</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -7791,10 +7780,10 @@
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
       <c r="AN7" s="3" t="n">
-        <v>0.06336097314022338</v>
+        <v>0.02027751002917078</v>
       </c>
       <c r="AO7" s="3" t="n">
-        <v>-0.004593434956671416</v>
+        <v>-0.004450505083797629</v>
       </c>
     </row>
     <row r="8">
@@ -7840,34 +7829,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>43889</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>44075</v>
+      </c>
+      <c r="M8" t="n">
+        <v>136</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.1195800593377413</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.1195800593377413</v>
+      </c>
+      <c r="P8" t="n">
+        <v>135</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.07004471576271205</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.03765706691064431</v>
+      </c>
+      <c r="S8" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>44995</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>45019</v>
-      </c>
-      <c r="M8" t="n">
-        <v>313</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>-0.06972871986006512</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>-0.1129718168111257</v>
-      </c>
-      <c r="P8" t="n">
-        <v>151</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.05148947965219722</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.03256480624756752</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -7877,40 +7866,40 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>297</v>
+        <v>7</v>
       </c>
       <c r="X8" t="n">
-        <v>102</v>
+        <v>-16</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.06972871986006512</v>
+        <v>-0.1195800593377413</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.1129718168111257</v>
+        <v>-0.1195800593377413</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>16</v>
+        <v>129</v>
       </c>
       <c r="AC8" t="n">
-        <v>-204</v>
+        <v>74</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.07495525375090195</v>
+        <v>0.1358216162707448</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.06082129671711477</v>
+        <v>-0.02361004736677749</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.1680311568208593</v>
+        <v>0.1763705613008727</v>
       </c>
       <c r="AH8" t="n">
-        <v>-182</v>
+        <v>26</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
@@ -7919,12 +7908,8 @@
       <c r="AK8" s="3" t="inlineStr"/>
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr"/>
-      <c r="AN8" s="3" t="n">
-        <v>0.06336097314022338</v>
-      </c>
-      <c r="AO8" s="3" t="n">
-        <v>-0.05953790568057138</v>
-      </c>
+      <c r="AN8" s="3" t="inlineStr"/>
+      <c r="AO8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7969,34 +7954,34 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>44067</v>
+      </c>
+      <c r="M9" t="n">
+        <v>130</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.2918967743785572</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.2918967743785572</v>
+      </c>
+      <c r="P9" t="n">
+        <v>129</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.1183655577125906</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.06222599155908312</v>
+      </c>
+      <c r="S9" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>45293</v>
-      </c>
-      <c r="M9" t="n">
-        <v>501</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>-0.2275727539629055</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>-0.2275727539629055</v>
-      </c>
-      <c r="P9" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.1214611782756227</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>0.09713025301409862</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -8006,40 +7991,40 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.2275727539629055</v>
+        <v>-0.2918967743785572</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.2275727539629055</v>
+        <v>-0.2918967743785572</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>306</v>
+        <v>107</v>
       </c>
       <c r="AC9" t="n">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.2946203090717709</v>
+        <v>0.412223477900957</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.003744150049416334</v>
+        <v>0.0009588772816613231</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.01018712271801892</v>
+        <v>0.004053846260056782</v>
       </c>
       <c r="AH9" t="n">
-        <v>108</v>
+        <v>4</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -8048,12 +8033,8 @@
       <c r="AK9" s="3" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
-      <c r="AN9" s="3" t="n">
-        <v>0.06336097314022338</v>
-      </c>
-      <c r="AO9" s="3" t="n">
-        <v>-0.004259490730372684</v>
-      </c>
+      <c r="AN9" s="3" t="inlineStr"/>
+      <c r="AO9" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8350,34 +8331,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>44931</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>45250</v>
+      </c>
+      <c r="M2" t="n">
+        <v>473</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.3239608533428741</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.3239608533428741</v>
+      </c>
+      <c r="P2" t="n">
+        <v>472</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.1873955345996986</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.1456175032694572</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>45835</v>
-      </c>
-      <c r="M2" t="n">
-        <v>89</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.2242012270138081</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.2242012270138081</v>
-      </c>
-      <c r="P2" t="n">
-        <v>88</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.1032426212645823</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.06633642004451878</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -8387,22 +8368,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>34</v>
+        <v>253</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.2242012270138081</v>
+        <v>-0.3239608533428741</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.2242012270138081</v>
+        <v>-0.3239608533428741</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>55</v>
+        <v>220</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -8411,7 +8392,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.2889940469367029</v>
+        <v>0.4792042812088524</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -8459,34 +8440,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>45135</v>
+      </c>
+      <c r="M3" t="n">
+        <v>393</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.2377598766809245</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.2377598766809245</v>
+      </c>
+      <c r="P3" t="n">
+        <v>392</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.1318162553441144</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.09338610296468229</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>45904</v>
-      </c>
-      <c r="M3" t="n">
-        <v>136</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.1513632279065376</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.1513632279065376</v>
-      </c>
-      <c r="P3" t="n">
-        <v>135</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.06216000016109517</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.04927686199609638</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -8496,31 +8477,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.1513632279065376</v>
+        <v>-0.2377598766809245</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.1513632279065376</v>
+        <v>-0.2377598766809245</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>102</v>
+        <v>198</v>
       </c>
       <c r="AC3" t="n">
-        <v>47</v>
+        <v>-22</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.1783604398064753</v>
+        <v>0.3119225417387239</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -8584,12 +8565,1272 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>45301</v>
+      </c>
+      <c r="M4" t="n">
+        <v>507</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.2032134999970446</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.2173480216895393</v>
+      </c>
+      <c r="P4" t="n">
+        <v>476</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.1161029160879204</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.09339855465440339</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" s="3" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>195</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>-0.2032134999970446</v>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>-0.2173480216895393</v>
+      </c>
+      <c r="AA4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>312</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>92</v>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="3" t="n">
+        <v>0.2550413441948263</v>
+      </c>
+      <c r="AF4" s="3" t="n">
+        <v>1.245168972109634e-05</v>
+      </c>
+      <c r="AG4" s="3" t="n">
+        <v>0.03454637668387983</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>114</v>
+      </c>
+      <c r="AI4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" s="3" t="n">
+        <v>0.672706785284984</v>
+      </c>
+      <c r="AO4" s="3" t="n">
+        <v>-0.4013611977680653</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>45317</v>
+      </c>
+      <c r="M5" t="n">
+        <v>518</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.2400831038360258</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.2400831038360258</v>
+      </c>
+      <c r="P5" t="n">
+        <v>517</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.1332952539449779</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.1083835912081281</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" s="3" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>195</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>-0.2400831038360258</v>
+      </c>
+      <c r="Z5" s="3" t="n">
+        <v>-0.2400831038360258</v>
+      </c>
+      <c r="AA5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>323</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>103</v>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="3" t="n">
+        <v>0.3159333672510169</v>
+      </c>
+      <c r="AF5" s="3" t="n">
+        <v>0.01499748824344581</v>
+      </c>
+      <c r="AG5" s="3" t="n">
+        <v>-0.002323227155101359</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>125</v>
+      </c>
+      <c r="AI5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" s="3" t="n">
+        <v>0.672706785284984</v>
+      </c>
+      <c r="AO5" s="3" t="n">
+        <v>-0.04869290891591871</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>44586</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>45019</v>
+      </c>
+      <c r="M6" t="n">
+        <v>313</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.08708938851250325</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.08708938851250325</v>
+      </c>
+      <c r="P6" t="n">
+        <v>312</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.03986676943861766</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.02521395887576482</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" s="3" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>15</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-180</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>-0.08708938851250325</v>
+      </c>
+      <c r="Z6" s="3" t="n">
+        <v>-0.08708938851250325</v>
+      </c>
+      <c r="AA6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>298</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>78</v>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="3" t="n">
+        <v>0.09539749830555677</v>
+      </c>
+      <c r="AF6" s="3" t="n">
+        <v>-0.06817214408891747</v>
+      </c>
+      <c r="AG6" s="3" t="n">
+        <v>0.1506704881684212</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>100</v>
+      </c>
+      <c r="AI6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" s="3" t="n">
+        <v>0.06336097314022338</v>
+      </c>
+      <c r="AO6" s="3" t="n">
+        <v>-0.06047836550494423</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>44729</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>45152</v>
+      </c>
+      <c r="M7" t="n">
+        <v>404</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.2205813583428692</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.2205813583428692</v>
+      </c>
+      <c r="P7" t="n">
+        <v>403</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.1274788262297419</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.09156526133515572</v>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" s="3" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>115</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-80</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>-0.2205813583428692</v>
+      </c>
+      <c r="Z7" s="3" t="n">
+        <v>-0.2205813583428692</v>
+      </c>
+      <c r="AA7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>289</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>69</v>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="3" t="n">
+        <v>0.2830075476176559</v>
+      </c>
+      <c r="AF7" s="3" t="n">
+        <v>-0.001820841629526573</v>
+      </c>
+      <c r="AG7" s="3" t="n">
+        <v>0.01717851833805528</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>91</v>
+      </c>
+      <c r="AI7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" s="3" t="n">
+        <v>0.06336097314022338</v>
+      </c>
+      <c r="AO7" s="3" t="n">
+        <v>-0.004593434956671416</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>44995</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>45019</v>
+      </c>
+      <c r="M8" t="n">
+        <v>313</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.06972871986006512</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.1129718168111257</v>
+      </c>
+      <c r="P8" t="n">
+        <v>151</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.05148947965219722</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.03256480624756752</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="T8" t="b">
+        <v>0</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" s="3" t="inlineStr"/>
+      <c r="W8" t="n">
+        <v>297</v>
+      </c>
+      <c r="X8" t="n">
+        <v>102</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>-0.06972871986006512</v>
+      </c>
+      <c r="Z8" s="3" t="n">
+        <v>-0.1129718168111257</v>
+      </c>
+      <c r="AA8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-204</v>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="3" t="n">
+        <v>0.07495525375090195</v>
+      </c>
+      <c r="AF8" s="3" t="n">
+        <v>-0.06082129671711477</v>
+      </c>
+      <c r="AG8" s="3" t="n">
+        <v>0.1680311568208593</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-182</v>
+      </c>
+      <c r="AI8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" s="3" t="n">
+        <v>0.06336097314022338</v>
+      </c>
+      <c r="AO8" s="3" t="n">
+        <v>-0.05953790568057138</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>45293</v>
+      </c>
+      <c r="M9" t="n">
+        <v>501</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.2275727539629055</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.2275727539629055</v>
+      </c>
+      <c r="P9" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.1214611782756227</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.09713025301409862</v>
+      </c>
+      <c r="S9" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="T9" t="b">
+        <v>0</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" s="3" t="inlineStr"/>
+      <c r="W9" t="n">
+        <v>195</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3" t="n">
+        <v>-0.2275727539629055</v>
+      </c>
+      <c r="Z9" s="3" t="n">
+        <v>-0.2275727539629055</v>
+      </c>
+      <c r="AA9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>306</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>86</v>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="3" t="n">
+        <v>0.2946203090717709</v>
+      </c>
+      <c r="AF9" s="3" t="n">
+        <v>0.003744150049416334</v>
+      </c>
+      <c r="AG9" s="3" t="n">
+        <v>0.01018712271801892</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>108</v>
+      </c>
+      <c r="AI9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" s="3" t="n">
+        <v>0.06336097314022338</v>
+      </c>
+      <c r="AO9" s="3" t="n">
+        <v>-0.004259490730372684</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AO9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="19" customWidth="1" min="18" max="18"/>
+    <col width="17" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="21" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="24" customWidth="1" min="27" max="27"/>
+    <col width="10" customWidth="1" min="28" max="28"/>
+    <col width="19" customWidth="1" min="29" max="29"/>
+    <col width="23" customWidth="1" min="30" max="30"/>
+    <col width="20" customWidth="1" min="31" max="31"/>
+    <col width="19" customWidth="1" min="32" max="32"/>
+    <col width="18" customWidth="1" min="33" max="33"/>
+    <col width="17" customWidth="1" min="34" max="34"/>
+    <col width="21" customWidth="1" min="35" max="35"/>
+    <col width="17" customWidth="1" min="36" max="36"/>
+    <col width="16" customWidth="1" min="37" max="37"/>
+    <col width="15" customWidth="1" min="38" max="38"/>
+    <col width="19" customWidth="1" min="39" max="39"/>
+    <col width="14" customWidth="1" min="40" max="40"/>
+    <col width="17" customWidth="1" min="41" max="41"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>base_run</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>fallback_run</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>detector</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>crisis_target</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>peak_date</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>trough_date</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>recovery_date</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_days</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>full_anchored_dd</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>full_hwm_dd</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_days_underwater</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer_common</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>full_common_end</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>full_no_drawdown</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>full_not_recovered</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>full_gap_at_cutoff</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_days</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_days_vs_defined</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_depth</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_max_dd</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_trough_at_boundary</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_days</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_days_vs_bench</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_vs_bench_censored</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_return_to_even</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_base_ulcer</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_base_depth</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_base_days</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_base_censored</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_fb_ulcer</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_fb_depth</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_fb_days</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_fb_censored</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>missed_rally</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>pre_peak_d_base</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>market_cap</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>mcap_t_10</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>benchmark</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>45835</v>
+      </c>
+      <c r="M2" t="n">
+        <v>89</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.2242012270138081</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.2242012270138081</v>
+      </c>
+      <c r="P2" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.1032426212645823</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.06633642004451878</v>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" s="3" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>34</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="3" t="n">
+        <v>-0.2242012270138081</v>
+      </c>
+      <c r="Z2" s="3" t="n">
+        <v>-0.2242012270138081</v>
+      </c>
+      <c r="AA2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="3" t="n">
+        <v>0.2889940469367029</v>
+      </c>
+      <c r="AF2" s="3" t="inlineStr"/>
+      <c r="AG2" s="3" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" s="3" t="inlineStr"/>
+      <c r="AK2" s="3" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" s="3" t="inlineStr"/>
+      <c r="AO2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="M3" t="n">
+        <v>136</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.1513632279065376</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.1513632279065376</v>
+      </c>
+      <c r="P3" t="n">
+        <v>135</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.06216000016109517</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.04927686199609638</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" s="3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>34</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>-0.1513632279065376</v>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>-0.1513632279065376</v>
+      </c>
+      <c r="AA3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>102</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>47</v>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="3" t="n">
+        <v>0.1783604398064753</v>
+      </c>
+      <c r="AF3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" s="3" t="inlineStr"/>
+      <c r="AO3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="n">
         <v>45707</v>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>0</v>
@@ -9300,13 +10541,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -9412,24 +10653,22 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="E2" s="4" t="n">
-        <v>156</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>373</v>
-      </c>
+      <c r="E2" s="4" t="inlineStr"/>
+      <c r="F2" s="4" t="inlineStr"/>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2</v>
+      </c>
       <c r="J2" s="3" t="n">
-        <v>0.496398891966759</v>
+        <v>0.6444444444444445</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>2</v>
@@ -9460,20 +10699,20 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-131</v>
+        <v>155</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>523</v>
+        <v>373</v>
       </c>
       <c r="G3" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="3" t="n">
-        <v>0.7274709302325582</v>
+        <v>0.4963948973932335</v>
       </c>
       <c r="K3" t="n">
         <v>3</v>
@@ -9506,20 +10745,24 @@
           <t>C3</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="n">
+        <v>-131</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>523</v>
+      </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="3" t="n">
-        <v>0</v>
+        <v>0.7274709302325582</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
         <v>2</v>
@@ -9555,16 +10798,14 @@
         <v>0</v>
       </c>
       <c r="H5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" s="3" t="n">
-        <v>0.7540983606557377</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>2</v>
@@ -9594,24 +10835,22 @@
           <t>C5</t>
         </is>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>-442</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>-174</v>
-      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>442</v>
+        <v>0</v>
       </c>
       <c r="H6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>8</v>
+      </c>
       <c r="J6" s="3" t="n">
-        <v>0.2787524366471735</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -9642,21 +10881,23 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-114</v>
-      </c>
-      <c r="F7" s="4" t="inlineStr"/>
+        <v>-442</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>-174</v>
+      </c>
       <c r="G7" t="n">
-        <v>114</v>
+        <v>442</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" s="3" t="n">
-        <v>1</v>
+        <v>0.2787524366471735</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>2</v>
@@ -9673,37 +10914,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>changepoint</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>vix</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>156</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>18</v>
-      </c>
+        <v>-114</v>
+      </c>
+      <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" s="3" t="n">
-        <v>0.08476454293628809</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>2</v>
@@ -9730,27 +10969,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>39</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>81</v>
-      </c>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2</v>
+      </c>
       <c r="J9" s="3" t="n">
-        <v>0.3350290697674418</v>
+        <v>0.4777777777777778</v>
       </c>
       <c r="K9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
         <v>2</v>
@@ -9777,14 +11014,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>30</v>
+        <v>155</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -9794,10 +11031,10 @@
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" s="3" t="n">
-        <v>0.5517241379310345</v>
+        <v>0.08485856905158069</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="L10" t="n">
         <v>2</v>
@@ -9824,27 +11061,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-10</v>
+        <v>39</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H11" t="b">
         <v>0</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" s="3" t="n">
-        <v>0.7622950819672131</v>
+        <v>0.3350290697674418</v>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L11" t="n">
         <v>2</v>
@@ -9871,27 +11108,27 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-21</v>
+        <v>31</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="G12" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H12" t="b">
         <v>0</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" s="3" t="n">
-        <v>0.4892787524366471</v>
+        <v>0.547945205479452</v>
       </c>
       <c r="K12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L12" t="n">
         <v>2</v>
@@ -9918,27 +11155,27 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>9</v>
+        <v>-10</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H13" t="b">
         <v>0</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" s="3" t="n">
-        <v>0.4772727272727273</v>
+        <v>0.7380952380952381</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L13" t="n">
         <v>2</v>
@@ -9955,37 +11192,37 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-35</v>
+        <v>-21</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>141</v>
+        <v>77</v>
       </c>
       <c r="G14" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="H14" t="b">
         <v>0</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" s="3" t="n">
-        <v>0.3634349030470914</v>
+        <v>0.4892787524366471</v>
       </c>
       <c r="K14" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="L14" t="n">
         <v>2</v>
@@ -10002,24 +11239,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>103</v>
+        <v>17</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -10029,10 +11266,10 @@
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" s="3" t="n">
-        <v>0.3960755813953488</v>
+        <v>0.4719101123595505</v>
       </c>
       <c r="K15" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="L15" t="n">
         <v>2</v>
@@ -10059,27 +11296,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>30</v>
+        <v>-52</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>27</v>
+        <v>317</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="H16" t="b">
         <v>0</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" s="3" t="n">
-        <v>0.4206896551724138</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>2</v>
@@ -10106,27 +11343,27 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>9</v>
+        <v>-36</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>93</v>
+        <v>141</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H17" t="b">
         <v>0</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" s="3" t="n">
-        <v>0.8770491803278688</v>
+        <v>0.3632834165280089</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="L17" t="n">
         <v>2</v>
@@ -10153,27 +11390,27 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-21</v>
+        <v>39</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="G18" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H18" t="b">
         <v>0</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" s="3" t="n">
-        <v>0.52046783625731</v>
+        <v>0.3960755813953488</v>
       </c>
       <c r="K18" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="L18" t="n">
         <v>2</v>
@@ -10200,14 +11437,14 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -10217,7 +11454,7 @@
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" s="3" t="n">
-        <v>0.4772727272727273</v>
+        <v>0.4178082191780822</v>
       </c>
       <c r="K19" t="n">
         <v>2</v>
@@ -10226,6 +11463,147 @@
         <v>2</v>
       </c>
       <c r="M19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>93</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" s="3" t="n">
+        <v>0.8492063492063492</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>-21</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>77</v>
+      </c>
+      <c r="G21" t="n">
+        <v>21</v>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" s="3" t="n">
+        <v>0.52046783625731</v>
+      </c>
+      <c r="K21" t="n">
+        <v>5</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" s="3" t="n">
+        <v>0.4719101123595505</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" t="b">
         <v>1</v>
       </c>
     </row>
